--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/Learn-AI-MCP_ML/SAP-C03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/AWS-Exam-Certificate-Preparation/SAP-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1150" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D0CCD2-DFBF-4B00-8F66-229D1C4A5F81}"/>
+  <xr:revisionPtr revIDLastSave="1157" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D415B8D-4240-4E53-B0CC-0E374B077870}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
   <sheets>
     <sheet name="ExamTopics" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="536">
   <si>
     <t>No</t>
   </si>
@@ -50,12 +50,6 @@
   </si>
   <si>
     <t>S.No</t>
-  </si>
-  <si>
-    <t>ExamTopics SOA-C03</t>
-  </si>
-  <si>
-    <t>ExamTopics SOA-C02</t>
   </si>
   <si>
     <t>URL</t>
@@ -2177,7 +2171,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2187,30 +2180,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="B1" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C1" s="6"/>
       <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="str">
         <f>TEXT(COUNTIF(B5:B242,"Yes")/COUNTA(B5:B242),"0.00%")</f>
-        <v>70.97%</v>
+        <v>60.00%</v>
       </c>
       <c r="C2" t="str">
         <f>TEXT(COUNTIF(C5:C242,"Yes")/COUNTA(C5:C242),"0.00%")</f>
-        <v>54.93%</v>
+        <v>0.00%</v>
       </c>
       <c r="D2" t="str">
         <f>TEXT(COUNTIF(D5:D242,"Yes")/COUNTA(D5:D242),"0.00%")</f>
-        <v>61.29%</v>
+        <v>0.00%</v>
       </c>
       <c r="E2" t="str">
         <f>TEXT(COUNTIF(E5:E242,"Yes")/COUNTA(E5:E242),"0.00%")</f>
-        <v>88.78%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2219,19 +2211,19 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIF(B6:B243,"Yes")</f>
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4">
         <f>COUNTIF(C6:C243,"Yes")</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4">
         <f>COUNTIF(D6:D243,"Yes")</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4">
         <f>COUNTIF(E6:E243,"Yes")</f>
-        <v>174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2240,19 +2232,19 @@
       </c>
       <c r="B4" s="3">
         <f>COUNTIF(B7:B244,"No")</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
         <f>COUNTIF(C7:C244,"No")</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
         <f>COUNTIF(D7:D244,"No")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
         <f>COUNTIF(E7:E244,"No")</f>
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2272,2169 +2264,1200 @@
         <v>2092026</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>14</v>
       </c>
-      <c r="B19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>15</v>
       </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>16</v>
       </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>17</v>
       </c>
-      <c r="B22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>18</v>
       </c>
-      <c r="B23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>20</v>
       </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>21</v>
       </c>
-      <c r="B26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>23</v>
       </c>
-      <c r="B28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>24</v>
       </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>25</v>
       </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>26</v>
       </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>27</v>
       </c>
-      <c r="B32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>28</v>
       </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>29</v>
       </c>
-      <c r="B34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>30</v>
       </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>31</v>
       </c>
-      <c r="C36" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>32</v>
       </c>
-      <c r="C37" t="s">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>33</v>
       </c>
-      <c r="C38" t="s">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>34</v>
       </c>
-      <c r="C39" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>35</v>
       </c>
-      <c r="C40" t="s">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>36</v>
       </c>
-      <c r="C41" t="s">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>37</v>
       </c>
-      <c r="C42" t="s">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>38</v>
       </c>
-      <c r="C43" t="s">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>39</v>
       </c>
-      <c r="C44" t="s">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>40</v>
       </c>
-      <c r="C45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>41</v>
       </c>
-      <c r="C46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>42</v>
       </c>
-      <c r="C47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>43</v>
       </c>
-      <c r="C48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>44</v>
       </c>
-      <c r="C49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45</v>
       </c>
-      <c r="C50" t="s">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46</v>
       </c>
-      <c r="C51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>47</v>
       </c>
-      <c r="C52" t="s">
-        <v>0</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>48</v>
       </c>
-      <c r="C53" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>49</v>
       </c>
-      <c r="C54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>50</v>
       </c>
-      <c r="C55" t="s">
-        <v>0</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>51</v>
       </c>
-      <c r="C56" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>52</v>
       </c>
-      <c r="C57" t="s">
-        <v>0</v>
-      </c>
-      <c r="E57" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>53</v>
       </c>
-      <c r="C58" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>54</v>
       </c>
-      <c r="C59" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>55</v>
       </c>
-      <c r="C60" t="s">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>56</v>
       </c>
-      <c r="C61" t="s">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>57</v>
       </c>
-      <c r="C62" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>58</v>
       </c>
-      <c r="C63" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>59</v>
       </c>
-      <c r="C64" t="s">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>60</v>
       </c>
-      <c r="C65" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>61</v>
       </c>
-      <c r="C66" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>62</v>
       </c>
-      <c r="C67" t="s">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>63</v>
       </c>
-      <c r="C68" t="s">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>64</v>
       </c>
-      <c r="C69" t="s">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>65</v>
       </c>
-      <c r="C70" t="s">
-        <v>0</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>66</v>
       </c>
-      <c r="C71" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>67</v>
       </c>
-      <c r="C72" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>68</v>
       </c>
-      <c r="C73" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>69</v>
       </c>
-      <c r="C74" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>70</v>
       </c>
-      <c r="C75" t="s">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>71</v>
       </c>
-      <c r="D76" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>72</v>
       </c>
-      <c r="D77" t="s">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>73</v>
       </c>
-      <c r="D78" t="s">
-        <v>0</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>74</v>
       </c>
-      <c r="D79" t="s">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>75</v>
       </c>
-      <c r="D80" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>76</v>
       </c>
-      <c r="D81" t="s">
-        <v>1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>77</v>
       </c>
-      <c r="D82" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>78</v>
       </c>
-      <c r="D83" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>79</v>
       </c>
-      <c r="D84" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>80</v>
       </c>
-      <c r="D85" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>81</v>
       </c>
-      <c r="D86" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>82</v>
       </c>
-      <c r="D87" t="s">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>83</v>
       </c>
-      <c r="D88" t="s">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>84</v>
       </c>
-      <c r="D89" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>85</v>
       </c>
-      <c r="D90" t="s">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>86</v>
       </c>
-      <c r="D91" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>87</v>
       </c>
-      <c r="D92" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>88</v>
       </c>
-      <c r="D93" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>89</v>
       </c>
-      <c r="D94" t="s">
-        <v>1</v>
-      </c>
-      <c r="E94" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>90</v>
       </c>
-      <c r="D95" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>91</v>
       </c>
-      <c r="D96" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>92</v>
       </c>
-      <c r="D97" t="s">
-        <v>1</v>
-      </c>
-      <c r="E97" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>93</v>
       </c>
-      <c r="D98" t="s">
-        <v>0</v>
-      </c>
-      <c r="E98" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>94</v>
       </c>
-      <c r="D99" t="s">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>95</v>
       </c>
-      <c r="D100" t="s">
-        <v>0</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>96</v>
       </c>
-      <c r="D101" t="s">
-        <v>0</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>97</v>
       </c>
-      <c r="D102" t="s">
-        <v>1</v>
-      </c>
-      <c r="E102" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>98</v>
       </c>
-      <c r="D103" t="s">
-        <v>1</v>
-      </c>
-      <c r="E103" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>99</v>
       </c>
-      <c r="D104" t="s">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>100</v>
       </c>
-      <c r="D105" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>101</v>
       </c>
-      <c r="E106" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>102</v>
       </c>
-      <c r="E107" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>103</v>
       </c>
-      <c r="E108" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>104</v>
       </c>
-      <c r="E109" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>105</v>
       </c>
-      <c r="E110" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>106</v>
       </c>
-      <c r="E111" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>107</v>
       </c>
-      <c r="E112" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>108</v>
       </c>
-      <c r="E113" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>109</v>
       </c>
-      <c r="E114" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>110</v>
       </c>
-      <c r="E115" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>111</v>
       </c>
-      <c r="E116" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>112</v>
       </c>
-      <c r="E117" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>113</v>
       </c>
-      <c r="E118" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>114</v>
       </c>
-      <c r="E119" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>115</v>
       </c>
-      <c r="E120" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>116</v>
       </c>
-      <c r="E121" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>117</v>
       </c>
-      <c r="E122" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>118</v>
       </c>
-      <c r="E123" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>119</v>
       </c>
-      <c r="E124" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>120</v>
       </c>
-      <c r="E125" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>121</v>
       </c>
-      <c r="E126" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>122</v>
       </c>
-      <c r="E127" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>123</v>
       </c>
-      <c r="E128" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>124</v>
       </c>
-      <c r="E129" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>125</v>
       </c>
-      <c r="E130" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>126</v>
       </c>
-      <c r="E131" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>127</v>
       </c>
-      <c r="E132" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>128</v>
       </c>
-      <c r="E133" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>129</v>
       </c>
-      <c r="E134" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>130</v>
       </c>
-      <c r="E135" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>131</v>
       </c>
-      <c r="E136" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>132</v>
       </c>
-      <c r="E137" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>133</v>
       </c>
-      <c r="E138" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>134</v>
       </c>
-      <c r="E139" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>135</v>
       </c>
-      <c r="E140" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>136</v>
       </c>
-      <c r="E141" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>137</v>
       </c>
-      <c r="E142" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>138</v>
       </c>
-      <c r="E143" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>139</v>
       </c>
-      <c r="E144" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>140</v>
       </c>
-      <c r="E145" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>141</v>
       </c>
-      <c r="E146" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>142</v>
       </c>
-      <c r="E147" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>143</v>
       </c>
-      <c r="E148" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>144</v>
       </c>
-      <c r="E149" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>145</v>
       </c>
-      <c r="E150" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>146</v>
       </c>
-      <c r="E151" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>147</v>
       </c>
-      <c r="E152" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>148</v>
       </c>
-      <c r="E153" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>149</v>
       </c>
-      <c r="E154" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>150</v>
       </c>
-      <c r="E155" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>151</v>
       </c>
-      <c r="E156" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>152</v>
       </c>
-      <c r="E157" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>153</v>
       </c>
-      <c r="E158" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>154</v>
       </c>
-      <c r="E159" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>155</v>
       </c>
-      <c r="E160" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>156</v>
       </c>
-      <c r="E161" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>157</v>
       </c>
-      <c r="E162" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>158</v>
       </c>
-      <c r="E163" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>159</v>
       </c>
-      <c r="E164" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>160</v>
       </c>
-      <c r="E165" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>161</v>
       </c>
-      <c r="E166" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>162</v>
       </c>
-      <c r="E167" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>163</v>
       </c>
-      <c r="E168" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>164</v>
       </c>
-      <c r="E169" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>165</v>
       </c>
-      <c r="E170" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>166</v>
       </c>
-      <c r="E171" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>167</v>
       </c>
-      <c r="E172" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>168</v>
       </c>
-      <c r="E173" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>169</v>
       </c>
-      <c r="E174" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>170</v>
       </c>
-      <c r="E175" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>171</v>
       </c>
-      <c r="E176" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>172</v>
       </c>
-      <c r="E177" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>173</v>
       </c>
-      <c r="E178" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>174</v>
       </c>
-      <c r="E179" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>175</v>
       </c>
-      <c r="E180" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>176</v>
       </c>
-      <c r="E181" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>177</v>
       </c>
-      <c r="E182" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>178</v>
       </c>
-      <c r="E183" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>179</v>
       </c>
-      <c r="E184" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>180</v>
       </c>
-      <c r="E185" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>181</v>
       </c>
-      <c r="E186" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>182</v>
       </c>
-      <c r="E187" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>183</v>
       </c>
-      <c r="E188" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>184</v>
       </c>
-      <c r="E189" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>185</v>
       </c>
-      <c r="E190" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>186</v>
       </c>
-      <c r="E191" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>187</v>
       </c>
-      <c r="E192" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>188</v>
       </c>
-      <c r="E193" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>189</v>
       </c>
-      <c r="E194" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>190</v>
       </c>
-      <c r="E195" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>191</v>
       </c>
-      <c r="E196" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>192</v>
       </c>
-      <c r="E197" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>193</v>
       </c>
-      <c r="E198" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>194</v>
       </c>
-      <c r="E199" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>195</v>
       </c>
-      <c r="E200" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="209" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="211" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="212" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="213" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="214" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="215" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="216" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="217" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="218" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="219" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>214</v>
       </c>
     </row>
-    <row r="220" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="221" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>217</v>
       </c>
     </row>
-    <row r="223" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>219</v>
       </c>
     </row>
-    <row r="225" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="226" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="227" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="228" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="229" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="230" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="231" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="232" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="233" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="234" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="235" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="236" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="237" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>233</v>
       </c>
     </row>
-    <row r="239" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>234</v>
       </c>
     </row>
-    <row r="240" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="241" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>236</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E241" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="No"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A5:E241" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}"/>
   <conditionalFormatting sqref="C6:C75 B6:B1048576 D76:D105">
     <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",B6)))</formula>
@@ -4469,13 +3492,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -4483,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -4491,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -4499,7 +3522,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -4507,7 +3530,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -4515,7 +3538,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -4523,7 +3546,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -4531,7 +3554,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -4539,7 +3562,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -4547,7 +3570,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -4555,7 +3578,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -4563,7 +3586,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -4571,7 +3594,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -4579,7 +3602,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -4587,7 +3610,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -4595,7 +3618,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -4603,7 +3626,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -4611,7 +3634,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -4619,7 +3642,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -4627,7 +3650,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -4635,7 +3658,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -4643,7 +3666,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -4651,7 +3674,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -4659,7 +3682,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -4667,7 +3690,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -4675,7 +3698,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -4683,7 +3706,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -4691,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -4699,7 +3722,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -4707,7 +3730,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -4715,7 +3738,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -4723,7 +3746,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -4731,7 +3754,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -4739,7 +3762,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -4747,7 +3770,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -4755,7 +3778,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -4763,7 +3786,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -4771,7 +3794,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -4779,7 +3802,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -4787,7 +3810,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -4795,7 +3818,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -4803,7 +3826,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -4811,7 +3834,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -4819,7 +3842,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -4827,7 +3850,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -4835,7 +3858,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -4843,7 +3866,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -4851,7 +3874,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -4859,7 +3882,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -4867,7 +3890,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -4875,7 +3898,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -4883,7 +3906,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -4891,7 +3914,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -4899,7 +3922,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -4907,7 +3930,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -4915,7 +3938,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -4923,7 +3946,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -4931,7 +3954,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -4939,7 +3962,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -4947,7 +3970,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -4955,7 +3978,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -4963,7 +3986,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -4971,7 +3994,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -4979,7 +4002,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -4987,7 +4010,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -4995,7 +4018,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -5003,7 +4026,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -5011,7 +4034,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -5019,7 +4042,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -5027,7 +4050,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -5035,7 +4058,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -5043,7 +4066,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -5051,7 +4074,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -5059,7 +4082,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -5067,7 +4090,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -5075,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -5083,7 +4106,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -5091,7 +4114,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -5099,7 +4122,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -5107,7 +4130,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -5115,7 +4138,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -5123,7 +4146,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -5131,7 +4154,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -5139,7 +4162,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -5147,7 +4170,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -5155,7 +4178,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -5163,7 +4186,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -5171,7 +4194,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -5179,7 +4202,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -5187,7 +4210,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -5195,7 +4218,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -5203,7 +4226,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -5211,7 +4234,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -5219,7 +4242,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -5227,7 +4250,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -5235,7 +4258,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -5243,7 +4266,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -5251,7 +4274,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -5259,7 +4282,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -5267,7 +4290,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -5275,7 +4298,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -5283,7 +4306,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -5291,7 +4314,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -5299,7 +4322,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -5307,7 +4330,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -5315,7 +4338,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -5323,7 +4346,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
@@ -5331,7 +4354,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -5339,7 +4362,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -5347,7 +4370,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
@@ -5355,7 +4378,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -5363,7 +4386,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -5371,7 +4394,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
@@ -5379,7 +4402,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -5387,7 +4410,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
@@ -5395,7 +4418,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
@@ -5403,7 +4426,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
@@ -5411,7 +4434,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
@@ -5419,7 +4442,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -5427,7 +4450,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
@@ -5435,7 +4458,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -5443,7 +4466,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -5451,7 +4474,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -5459,7 +4482,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
@@ -5467,7 +4490,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -5475,7 +4498,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -5483,7 +4506,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
@@ -5491,7 +4514,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
@@ -5499,7 +4522,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
@@ -5507,7 +4530,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
@@ -5515,7 +4538,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
@@ -5523,7 +4546,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
@@ -5531,7 +4554,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
@@ -5539,7 +4562,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -5547,7 +4570,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
@@ -5555,7 +4578,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -5563,7 +4586,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
@@ -5571,7 +4594,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
@@ -5579,7 +4602,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
@@ -5587,7 +4610,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
@@ -5595,7 +4618,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
@@ -5603,7 +4626,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
@@ -5611,7 +4634,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
@@ -5619,7 +4642,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -5627,7 +4650,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -5635,7 +4658,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
@@ -5643,7 +4666,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -5651,7 +4674,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -5659,7 +4682,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -5667,7 +4690,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
@@ -5675,7 +4698,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -5683,7 +4706,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
@@ -5691,7 +4714,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -5699,7 +4722,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -5707,7 +4730,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -5715,7 +4738,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -5723,7 +4746,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
@@ -5731,7 +4754,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
@@ -5739,7 +4762,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
@@ -5747,7 +4770,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
@@ -5755,7 +4778,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -5763,7 +4786,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -5771,7 +4794,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
@@ -5779,7 +4802,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
@@ -5787,7 +4810,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
@@ -5795,7 +4818,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -5803,7 +4826,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -5811,7 +4834,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
@@ -5819,7 +4842,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -5827,7 +4850,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
@@ -5835,7 +4858,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
@@ -5843,7 +4866,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -5851,7 +4874,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
@@ -5859,7 +4882,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -5867,7 +4890,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -5875,7 +4898,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -5883,7 +4906,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
@@ -5891,7 +4914,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
@@ -5899,7 +4922,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
@@ -5907,7 +4930,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
@@ -5915,7 +4938,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
@@ -5923,7 +4946,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
@@ -5931,7 +4954,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
@@ -5939,7 +4962,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
@@ -5947,7 +4970,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
@@ -5955,7 +4978,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
@@ -5963,7 +4986,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
@@ -5971,7 +4994,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
@@ -5979,7 +5002,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
@@ -5987,7 +5010,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -5995,7 +5018,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
@@ -6003,7 +5026,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
@@ -6011,7 +5034,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
@@ -6019,7 +5042,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
@@ -6027,7 +5050,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
@@ -6035,7 +5058,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
@@ -6043,7 +5066,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
@@ -6051,7 +5074,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
@@ -6059,7 +5082,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
@@ -6067,7 +5090,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
@@ -6075,7 +5098,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
@@ -6083,7 +5106,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
@@ -6091,7 +5114,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
@@ -6099,7 +5122,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
@@ -6107,7 +5130,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
@@ -6115,7 +5138,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
@@ -6123,7 +5146,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
@@ -6131,7 +5154,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
@@ -6139,7 +5162,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -6147,7 +5170,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -6155,7 +5178,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
@@ -6163,7 +5186,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
@@ -6171,7 +5194,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
@@ -6179,7 +5202,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
@@ -6187,7 +5210,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
@@ -6195,7 +5218,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
@@ -6203,7 +5226,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
@@ -6211,7 +5234,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
@@ -6219,7 +5242,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
@@ -6227,7 +5250,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
@@ -6235,7 +5258,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
@@ -6243,7 +5266,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
@@ -6251,7 +5274,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
@@ -6259,7 +5282,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
@@ -6267,7 +5290,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
@@ -6275,7 +5298,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
@@ -6283,7 +5306,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
@@ -6291,7 +5314,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
@@ -6299,7 +5322,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
@@ -6307,7 +5330,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
@@ -6315,7 +5338,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
@@ -6323,7 +5346,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
@@ -6331,7 +5354,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -6339,7 +5362,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
@@ -6347,7 +5370,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
@@ -6355,7 +5378,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
@@ -6363,7 +5386,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
@@ -6371,7 +5394,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
@@ -6379,7 +5402,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
@@ -6387,7 +5410,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
@@ -6395,7 +5418,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
@@ -6403,7 +5426,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
@@ -6411,7 +5434,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
@@ -6419,7 +5442,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
@@ -6427,7 +5450,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
@@ -6435,7 +5458,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
@@ -6443,7 +5466,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
@@ -6451,7 +5474,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
@@ -6459,7 +5482,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
@@ -6467,7 +5490,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
@@ -6475,7 +5498,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
@@ -6483,7 +5506,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
@@ -6491,7 +5514,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
@@ -6499,7 +5522,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
@@ -6507,7 +5530,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
@@ -6515,7 +5538,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
@@ -6523,7 +5546,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
@@ -6531,7 +5554,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
@@ -6539,7 +5562,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
@@ -6547,7 +5570,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
@@ -6555,7 +5578,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
@@ -6563,7 +5586,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
@@ -6571,7 +5594,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
@@ -6579,7 +5602,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
@@ -6587,7 +5610,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
@@ -6595,7 +5618,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
@@ -6603,7 +5626,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
@@ -6611,7 +5634,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
@@ -6619,7 +5642,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
@@ -6627,7 +5650,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
@@ -6635,7 +5658,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
@@ -6643,7 +5666,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
@@ -6651,7 +5674,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
@@ -6659,7 +5682,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
@@ -6667,7 +5690,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
@@ -6675,7 +5698,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
@@ -6683,7 +5706,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
@@ -6691,7 +5714,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
@@ -6699,7 +5722,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
@@ -6707,7 +5730,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
@@ -6715,7 +5738,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
@@ -6723,7 +5746,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
@@ -6731,7 +5754,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
@@ -6739,7 +5762,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
@@ -6747,7 +5770,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
@@ -6755,7 +5778,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
@@ -6763,7 +5786,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
@@ -6771,7 +5794,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
@@ -6779,7 +5802,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
@@ -6787,7 +5810,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
@@ -6795,7 +5818,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
@@ -6803,7 +5826,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
@@ -6811,7 +5834,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
@@ -6819,7 +5842,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
@@ -6827,7 +5850,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
@@ -6835,7 +5858,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
@@ -6843,7 +5866,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
@@ -6851,7 +5874,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
@@ -6859,7 +5882,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
@@ -6867,7 +5890,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
@@ -6875,7 +5898,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
@@ -6883,7 +5906,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
@@ -6891,7 +5914,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
@@ -6899,7 +5922,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
@@ -6907,7 +5930,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
@@ -6915,7 +5938,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
@@ -6923,7 +5946,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
@@ -6931,7 +5954,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
@@ -6939,7 +5962,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
@@ -6947,7 +5970,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
@@ -6955,7 +5978,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
@@ -6963,7 +5986,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
@@ -6971,7 +5994,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
@@ -6979,7 +6002,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
@@ -6987,7 +6010,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
@@ -6995,7 +6018,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
@@ -7003,7 +6026,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
@@ -7011,7 +6034,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
@@ -7019,7 +6042,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
@@ -7027,7 +6050,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
@@ -7035,7 +6058,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
@@ -7043,7 +6066,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
@@ -7051,7 +6074,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
@@ -7059,7 +6082,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
@@ -7067,7 +6090,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
@@ -7075,7 +6098,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
@@ -7083,7 +6106,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
@@ -7091,7 +6114,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
@@ -7099,7 +6122,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
@@ -7107,7 +6130,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
@@ -7115,7 +6138,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
@@ -7123,7 +6146,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
@@ -7131,7 +6154,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
@@ -7139,7 +6162,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
@@ -7147,7 +6170,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
@@ -7155,7 +6178,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
@@ -7163,7 +6186,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
@@ -7171,7 +6194,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
@@ -7179,7 +6202,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
@@ -7187,7 +6210,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
@@ -7195,7 +6218,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
@@ -7203,7 +6226,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
@@ -7211,7 +6234,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
@@ -7219,7 +6242,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
@@ -7227,7 +6250,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
@@ -7235,7 +6258,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
@@ -7243,7 +6266,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
@@ -7251,7 +6274,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
@@ -7259,7 +6282,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
@@ -7267,7 +6290,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
@@ -7275,7 +6298,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
@@ -7283,7 +6306,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
@@ -7291,7 +6314,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
@@ -7299,7 +6322,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
@@ -7307,7 +6330,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
@@ -7315,7 +6338,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
@@ -7323,7 +6346,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
@@ -7331,7 +6354,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
@@ -7339,7 +6362,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
@@ -7347,7 +6370,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
@@ -7355,7 +6378,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
@@ -7363,7 +6386,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
@@ -7371,7 +6394,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
@@ -7379,7 +6402,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
@@ -7387,7 +6410,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
@@ -7395,7 +6418,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
@@ -7403,7 +6426,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
@@ -7411,7 +6434,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
@@ -7419,7 +6442,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
@@ -7427,7 +6450,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
@@ -7435,7 +6458,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
@@ -7443,7 +6466,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
@@ -7451,7 +6474,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
@@ -7459,7 +6482,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
@@ -7467,7 +6490,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
@@ -7475,7 +6498,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
@@ -7483,7 +6506,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
@@ -7491,7 +6514,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
@@ -7499,7 +6522,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
@@ -7507,7 +6530,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
@@ -7515,7 +6538,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
@@ -7523,7 +6546,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
@@ -7531,7 +6554,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
@@ -7539,7 +6562,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
@@ -7547,7 +6570,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
@@ -7555,7 +6578,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
@@ -7563,7 +6586,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
@@ -7571,7 +6594,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
@@ -7579,7 +6602,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
@@ -7587,7 +6610,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
@@ -7595,7 +6618,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
@@ -7603,7 +6626,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
@@ -7611,7 +6634,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
@@ -7619,7 +6642,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
@@ -7627,7 +6650,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
@@ -7635,7 +6658,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
@@ -7643,7 +6666,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
@@ -7651,7 +6674,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
@@ -7659,7 +6682,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
@@ -7667,7 +6690,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
@@ -7675,7 +6698,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
@@ -7683,7 +6706,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
@@ -7691,7 +6714,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
@@ -7699,7 +6722,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
@@ -7707,7 +6730,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
@@ -7715,7 +6738,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
@@ -7723,7 +6746,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
@@ -7731,7 +6754,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
@@ -7739,7 +6762,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
@@ -7747,7 +6770,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
@@ -7755,7 +6778,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
@@ -7763,7 +6786,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
@@ -7771,7 +6794,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
@@ -7779,7 +6802,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
@@ -7787,7 +6810,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
@@ -7795,7 +6818,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
@@ -7803,7 +6826,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
@@ -7811,7 +6834,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
@@ -7819,7 +6842,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
@@ -7827,7 +6850,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
@@ -7835,7 +6858,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
@@ -7843,7 +6866,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
@@ -7851,7 +6874,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
@@ -7859,7 +6882,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
@@ -7867,7 +6890,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
@@ -7875,7 +6898,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
@@ -7883,7 +6906,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
@@ -7891,7 +6914,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
@@ -7899,7 +6922,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
@@ -7907,7 +6930,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
@@ -7915,7 +6938,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
@@ -7923,7 +6946,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
@@ -7931,7 +6954,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
@@ -7939,7 +6962,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
@@ -7947,7 +6970,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
@@ -7955,7 +6978,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
@@ -7963,7 +6986,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
@@ -7971,7 +6994,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
@@ -7979,7 +7002,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
@@ -7987,7 +7010,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
@@ -7995,7 +7018,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
@@ -8003,7 +7026,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
@@ -8011,7 +7034,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
@@ -8019,7 +7042,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
@@ -8027,7 +7050,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
@@ -8035,7 +7058,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
@@ -8043,7 +7066,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
@@ -8051,7 +7074,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
@@ -8059,7 +7082,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
@@ -8067,7 +7090,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
@@ -8075,7 +7098,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
@@ -8083,7 +7106,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
@@ -8091,7 +7114,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
@@ -8099,7 +7122,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
@@ -8107,7 +7130,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
@@ -8115,7 +7138,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
@@ -8123,7 +7146,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
@@ -8131,7 +7154,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
@@ -8139,7 +7162,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
@@ -8147,7 +7170,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
@@ -8155,7 +7178,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
@@ -8163,7 +7186,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
@@ -8171,7 +7194,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
@@ -8179,7 +7202,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
@@ -8187,7 +7210,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
@@ -8195,7 +7218,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
@@ -8203,7 +7226,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
@@ -8211,7 +7234,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
@@ -8219,7 +7242,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
@@ -8227,7 +7250,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
@@ -8235,7 +7258,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
@@ -8243,7 +7266,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
@@ -8251,7 +7274,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
@@ -8259,7 +7282,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
@@ -8267,7 +7290,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
@@ -8275,7 +7298,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
@@ -8283,7 +7306,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
@@ -8291,7 +7314,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
@@ -8299,7 +7322,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
@@ -8307,7 +7330,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
@@ -8315,7 +7338,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
@@ -8323,7 +7346,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
@@ -8331,7 +7354,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
@@ -8339,7 +7362,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
@@ -8347,7 +7370,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
@@ -8355,7 +7378,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
@@ -8363,7 +7386,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
@@ -8371,7 +7394,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
@@ -8379,7 +7402,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
@@ -8387,7 +7410,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
@@ -8395,7 +7418,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
@@ -8403,7 +7426,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
@@ -8411,7 +7434,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
@@ -8419,7 +7442,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
@@ -8427,7 +7450,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
@@ -8435,7 +7458,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
@@ -8443,7 +7466,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
@@ -8451,7 +7474,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
@@ -8459,7 +7482,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
@@ -8467,7 +7490,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
@@ -8475,7 +7498,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
@@ -8483,7 +7506,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
@@ -8491,7 +7514,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
@@ -8499,7 +7522,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
@@ -8507,7 +7530,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
@@ -8515,7 +7538,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
@@ -8523,7 +7546,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
@@ -8531,7 +7554,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
@@ -8539,7 +7562,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
@@ -8547,7 +7570,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
@@ -8555,7 +7578,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
@@ -8563,7 +7586,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
@@ -8571,7 +7594,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
@@ -8579,7 +7602,7 @@
         <v>512</v>
       </c>
       <c r="B514" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
@@ -8587,7 +7610,7 @@
         <v>513</v>
       </c>
       <c r="B515" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
@@ -8595,7 +7618,7 @@
         <v>514</v>
       </c>
       <c r="B516" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
@@ -8603,7 +7626,7 @@
         <v>515</v>
       </c>
       <c r="B517" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
@@ -8611,7 +7634,7 @@
         <v>516</v>
       </c>
       <c r="B518" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
@@ -8619,7 +7642,7 @@
         <v>517</v>
       </c>
       <c r="B519" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
@@ -8627,7 +7650,7 @@
         <v>518</v>
       </c>
       <c r="B520" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
@@ -8635,7 +7658,7 @@
         <v>519</v>
       </c>
       <c r="B521" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
@@ -8643,7 +7666,7 @@
         <v>520</v>
       </c>
       <c r="B522" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
@@ -8651,7 +7674,7 @@
         <v>521</v>
       </c>
       <c r="B523" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
@@ -8659,7 +7682,7 @@
         <v>522</v>
       </c>
       <c r="B524" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
@@ -8667,7 +7690,7 @@
         <v>523</v>
       </c>
       <c r="B525" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
@@ -8675,7 +7698,7 @@
         <v>524</v>
       </c>
       <c r="B526" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
@@ -8683,7 +7706,7 @@
         <v>525</v>
       </c>
       <c r="B527" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
@@ -8691,7 +7714,7 @@
         <v>526</v>
       </c>
       <c r="B528" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
@@ -8699,7 +7722,7 @@
         <v>527</v>
       </c>
       <c r="B529" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
@@ -8707,7 +7730,7 @@
         <v>528</v>
       </c>
       <c r="B530" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
@@ -8715,7 +7738,7 @@
         <v>529</v>
       </c>
       <c r="B531" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/AWS-Exam-Certificate-Preparation/SAP-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1157" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D415B8D-4240-4E53-B0CC-0E374B077870}"/>
+  <xr:revisionPtr revIDLastSave="1237" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942BFD94-C0E5-4B4E-8359-F2E487A90595}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExamTopics" sheetId="4" r:id="rId1"/>
+    <sheet name="ExamTopics" sheetId="4" state="hidden" r:id="rId1"/>
     <sheet name="ExamTopics (SAP-C02)" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -1759,7 +1759,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1785,6 +1785,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7105,7 +7106,7 @@
       <c r="A452" s="1">
         <v>450</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B452" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7113,7 +7114,7 @@
       <c r="A453" s="1">
         <v>451</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B453" s="9" t="s">
         <v>53</v>
       </c>
     </row>
@@ -7121,7 +7122,7 @@
       <c r="A454" s="1">
         <v>452</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B454" s="9" t="s">
         <v>502</v>
       </c>
     </row>
@@ -7129,7 +7130,7 @@
       <c r="A455" s="1">
         <v>453</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B455" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7137,7 +7138,7 @@
       <c r="A456" s="1">
         <v>454</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B456" s="9" t="s">
         <v>52</v>
       </c>
     </row>
@@ -7145,7 +7146,7 @@
       <c r="A457" s="1">
         <v>455</v>
       </c>
-      <c r="B457" t="s">
+      <c r="B457" s="9" t="s">
         <v>297</v>
       </c>
     </row>
@@ -7153,7 +7154,7 @@
       <c r="A458" s="1">
         <v>456</v>
       </c>
-      <c r="B458" t="s">
+      <c r="B458" s="9" t="s">
         <v>445</v>
       </c>
     </row>
@@ -7161,7 +7162,7 @@
       <c r="A459" s="1">
         <v>457</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B459" s="9" t="s">
         <v>430</v>
       </c>
     </row>
@@ -7169,7 +7170,7 @@
       <c r="A460" s="1">
         <v>458</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B460" s="9" t="s">
         <v>309</v>
       </c>
     </row>
@@ -7177,7 +7178,7 @@
       <c r="A461" s="1">
         <v>459</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="9" t="s">
         <v>464</v>
       </c>
     </row>
@@ -7185,7 +7186,7 @@
       <c r="A462" s="1">
         <v>460</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="9" t="s">
         <v>444</v>
       </c>
     </row>
@@ -7193,7 +7194,7 @@
       <c r="A463" s="1">
         <v>461</v>
       </c>
-      <c r="B463" t="s">
+      <c r="B463" s="9" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7201,7 +7202,7 @@
       <c r="A464" s="1">
         <v>462</v>
       </c>
-      <c r="B464" t="s">
+      <c r="B464" s="9" t="s">
         <v>424</v>
       </c>
     </row>
@@ -7209,7 +7210,7 @@
       <c r="A465" s="1">
         <v>463</v>
       </c>
-      <c r="B465" t="s">
+      <c r="B465" s="9" t="s">
         <v>495</v>
       </c>
     </row>
@@ -7217,7 +7218,7 @@
       <c r="A466" s="1">
         <v>464</v>
       </c>
-      <c r="B466" t="s">
+      <c r="B466" s="9" t="s">
         <v>401</v>
       </c>
     </row>
@@ -7225,7 +7226,7 @@
       <c r="A467" s="1">
         <v>465</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="9" t="s">
         <v>443</v>
       </c>
     </row>
@@ -7233,7 +7234,7 @@
       <c r="A468" s="1">
         <v>466</v>
       </c>
-      <c r="B468" t="s">
+      <c r="B468" s="9" t="s">
         <v>505</v>
       </c>
     </row>
@@ -7241,7 +7242,7 @@
       <c r="A469" s="1">
         <v>467</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B469" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7249,7 +7250,7 @@
       <c r="A470" s="1">
         <v>468</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B470" s="9" t="s">
         <v>442</v>
       </c>
     </row>
@@ -7257,7 +7258,7 @@
       <c r="A471" s="1">
         <v>469</v>
       </c>
-      <c r="B471" t="s">
+      <c r="B471" s="9" t="s">
         <v>441</v>
       </c>
     </row>
@@ -7265,7 +7266,7 @@
       <c r="A472" s="1">
         <v>470</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B472" s="9" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7273,7 +7274,7 @@
       <c r="A473" s="1">
         <v>471</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7281,7 +7282,7 @@
       <c r="A474" s="1">
         <v>472</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B474" s="9" t="s">
         <v>128</v>
       </c>
     </row>
@@ -7289,7 +7290,7 @@
       <c r="A475" s="1">
         <v>473</v>
       </c>
-      <c r="B475" t="s">
+      <c r="B475" s="9" t="s">
         <v>335</v>
       </c>
     </row>
@@ -7297,7 +7298,7 @@
       <c r="A476" s="1">
         <v>474</v>
       </c>
-      <c r="B476" t="s">
+      <c r="B476" s="9" t="s">
         <v>215</v>
       </c>
     </row>
@@ -7305,7 +7306,7 @@
       <c r="A477" s="1">
         <v>475</v>
       </c>
-      <c r="B477" t="s">
+      <c r="B477" s="9" t="s">
         <v>417</v>
       </c>
     </row>
@@ -7313,7 +7314,7 @@
       <c r="A478" s="1">
         <v>476</v>
       </c>
-      <c r="B478" t="s">
+      <c r="B478" s="9" t="s">
         <v>204</v>
       </c>
     </row>
@@ -7321,7 +7322,7 @@
       <c r="A479" s="1">
         <v>477</v>
       </c>
-      <c r="B479" t="s">
+      <c r="B479" s="9" t="s">
         <v>510</v>
       </c>
     </row>
@@ -7329,7 +7330,7 @@
       <c r="A480" s="1">
         <v>478</v>
       </c>
-      <c r="B480" t="s">
+      <c r="B480" s="9" t="s">
         <v>439</v>
       </c>
     </row>
@@ -7337,7 +7338,7 @@
       <c r="A481" s="1">
         <v>479</v>
       </c>
-      <c r="B481" t="s">
+      <c r="B481" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -7345,7 +7346,7 @@
       <c r="A482" s="1">
         <v>480</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B482" s="9" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7353,7 +7354,7 @@
       <c r="A483" s="1">
         <v>481</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B483" s="9" t="s">
         <v>465</v>
       </c>
     </row>
@@ -7361,7 +7362,7 @@
       <c r="A484" s="1">
         <v>482</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B484" s="9" t="s">
         <v>438</v>
       </c>
     </row>
@@ -7369,7 +7370,7 @@
       <c r="A485" s="1">
         <v>483</v>
       </c>
-      <c r="B485" t="s">
+      <c r="B485" s="9" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7377,7 +7378,7 @@
       <c r="A486" s="1">
         <v>484</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B486" s="9" t="s">
         <v>425</v>
       </c>
     </row>
@@ -7385,7 +7386,7 @@
       <c r="A487" s="1">
         <v>485</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B487" s="9" t="s">
         <v>468</v>
       </c>
     </row>
@@ -7393,7 +7394,7 @@
       <c r="A488" s="1">
         <v>486</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B488" s="9" t="s">
         <v>397</v>
       </c>
     </row>
@@ -7401,7 +7402,7 @@
       <c r="A489" s="1">
         <v>487</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B489" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7409,7 +7410,7 @@
       <c r="A490" s="1">
         <v>488</v>
       </c>
-      <c r="B490" t="s">
+      <c r="B490" s="9" t="s">
         <v>474</v>
       </c>
     </row>
@@ -7417,7 +7418,7 @@
       <c r="A491" s="1">
         <v>489</v>
       </c>
-      <c r="B491" t="s">
+      <c r="B491" s="9" t="s">
         <v>400</v>
       </c>
     </row>
@@ -7425,7 +7426,7 @@
       <c r="A492" s="1">
         <v>490</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B492" s="9" t="s">
         <v>426</v>
       </c>
     </row>
@@ -7433,7 +7434,7 @@
       <c r="A493" s="1">
         <v>491</v>
       </c>
-      <c r="B493" t="s">
+      <c r="B493" s="9" t="s">
         <v>345</v>
       </c>
     </row>
@@ -7441,7 +7442,7 @@
       <c r="A494" s="1">
         <v>492</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B494" s="9" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7449,7 +7450,7 @@
       <c r="A495" s="1">
         <v>493</v>
       </c>
-      <c r="B495" t="s">
+      <c r="B495" s="9" t="s">
         <v>343</v>
       </c>
     </row>
@@ -7457,7 +7458,7 @@
       <c r="A496" s="1">
         <v>494</v>
       </c>
-      <c r="B496" t="s">
+      <c r="B496" s="9" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7465,7 +7466,7 @@
       <c r="A497" s="1">
         <v>495</v>
       </c>
-      <c r="B497" t="s">
+      <c r="B497" s="9" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7473,7 +7474,7 @@
       <c r="A498" s="1">
         <v>496</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B498" s="9" t="s">
         <v>392</v>
       </c>
     </row>
@@ -7481,7 +7482,7 @@
       <c r="A499" s="1">
         <v>497</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B499" s="9" t="s">
         <v>507</v>
       </c>
     </row>
@@ -7489,7 +7490,7 @@
       <c r="A500" s="1">
         <v>498</v>
       </c>
-      <c r="B500" t="s">
+      <c r="B500" s="9" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7497,7 +7498,7 @@
       <c r="A501" s="1">
         <v>499</v>
       </c>
-      <c r="B501" t="s">
+      <c r="B501" s="9" t="s">
         <v>418</v>
       </c>
     </row>
@@ -7505,7 +7506,7 @@
       <c r="A502" s="1">
         <v>500</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B502" s="9" t="s">
         <v>166</v>
       </c>
     </row>
@@ -7513,7 +7514,7 @@
       <c r="A503" s="1">
         <v>501</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B503" s="9" t="s">
         <v>54</v>
       </c>
     </row>
@@ -7521,7 +7522,7 @@
       <c r="A504" s="1">
         <v>502</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B504" s="9" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7529,7 +7530,7 @@
       <c r="A505" s="1">
         <v>503</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="9" t="s">
         <v>55</v>
       </c>
     </row>
@@ -7537,7 +7538,7 @@
       <c r="A506" s="1">
         <v>504</v>
       </c>
-      <c r="B506" t="s">
+      <c r="B506" s="9" t="s">
         <v>393</v>
       </c>
     </row>
@@ -7545,7 +7546,7 @@
       <c r="A507" s="1">
         <v>505</v>
       </c>
-      <c r="B507" t="s">
+      <c r="B507" s="9" t="s">
         <v>521</v>
       </c>
     </row>
@@ -7553,7 +7554,7 @@
       <c r="A508" s="1">
         <v>506</v>
       </c>
-      <c r="B508" t="s">
+      <c r="B508" s="9" t="s">
         <v>56</v>
       </c>
     </row>
@@ -7561,7 +7562,7 @@
       <c r="A509" s="1">
         <v>507</v>
       </c>
-      <c r="B509" t="s">
+      <c r="B509" s="9" t="s">
         <v>135</v>
       </c>
     </row>
@@ -7569,7 +7570,7 @@
       <c r="A510" s="1">
         <v>508</v>
       </c>
-      <c r="B510" t="s">
+      <c r="B510" s="9" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7577,7 +7578,7 @@
       <c r="A511" s="1">
         <v>509</v>
       </c>
-      <c r="B511" t="s">
+      <c r="B511" s="9" t="s">
         <v>311</v>
       </c>
     </row>
@@ -7585,7 +7586,7 @@
       <c r="A512" s="1">
         <v>510</v>
       </c>
-      <c r="B512" t="s">
+      <c r="B512" s="9" t="s">
         <v>207</v>
       </c>
     </row>
@@ -7593,7 +7594,7 @@
       <c r="A513" s="1">
         <v>511</v>
       </c>
-      <c r="B513" t="s">
+      <c r="B513" s="9" t="s">
         <v>330</v>
       </c>
     </row>
@@ -7601,7 +7602,7 @@
       <c r="A514" s="1">
         <v>512</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B514" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -7609,7 +7610,7 @@
       <c r="A515" s="1">
         <v>513</v>
       </c>
-      <c r="B515" t="s">
+      <c r="B515" s="9" t="s">
         <v>497</v>
       </c>
     </row>
@@ -7617,7 +7618,7 @@
       <c r="A516" s="1">
         <v>514</v>
       </c>
-      <c r="B516" t="s">
+      <c r="B516" s="9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7625,7 +7626,7 @@
       <c r="A517" s="1">
         <v>515</v>
       </c>
-      <c r="B517" t="s">
+      <c r="B517" s="9" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7633,7 +7634,7 @@
       <c r="A518" s="1">
         <v>516</v>
       </c>
-      <c r="B518" t="s">
+      <c r="B518" s="9" t="s">
         <v>353</v>
       </c>
     </row>
@@ -7641,7 +7642,7 @@
       <c r="A519" s="1">
         <v>517</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B519" s="9" t="s">
         <v>380</v>
       </c>
     </row>
@@ -7649,7 +7650,7 @@
       <c r="A520" s="1">
         <v>518</v>
       </c>
-      <c r="B520" t="s">
+      <c r="B520" s="9" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7657,7 +7658,7 @@
       <c r="A521" s="1">
         <v>519</v>
       </c>
-      <c r="B521" t="s">
+      <c r="B521" s="9" t="s">
         <v>432</v>
       </c>
     </row>
@@ -7665,7 +7666,7 @@
       <c r="A522" s="1">
         <v>520</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B522" s="9" t="s">
         <v>508</v>
       </c>
     </row>
@@ -7673,7 +7674,7 @@
       <c r="A523" s="1">
         <v>521</v>
       </c>
-      <c r="B523" t="s">
+      <c r="B523" s="9" t="s">
         <v>408</v>
       </c>
     </row>
@@ -7681,7 +7682,7 @@
       <c r="A524" s="1">
         <v>522</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B524" s="9" t="s">
         <v>341</v>
       </c>
     </row>
@@ -7689,7 +7690,7 @@
       <c r="A525" s="1">
         <v>523</v>
       </c>
-      <c r="B525" t="s">
+      <c r="B525" s="9" t="s">
         <v>376</v>
       </c>
     </row>
@@ -7697,7 +7698,7 @@
       <c r="A526" s="1">
         <v>524</v>
       </c>
-      <c r="B526" t="s">
+      <c r="B526" s="9" t="s">
         <v>312</v>
       </c>
     </row>
@@ -7705,7 +7706,7 @@
       <c r="A527" s="1">
         <v>525</v>
       </c>
-      <c r="B527" t="s">
+      <c r="B527" s="9" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7713,7 +7714,7 @@
       <c r="A528" s="1">
         <v>526</v>
       </c>
-      <c r="B528" t="s">
+      <c r="B528" s="9" t="s">
         <v>220</v>
       </c>
     </row>
@@ -7721,7 +7722,7 @@
       <c r="A529" s="1">
         <v>527</v>
       </c>
-      <c r="B529" t="s">
+      <c r="B529" s="9" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7729,7 +7730,7 @@
       <c r="A530" s="1">
         <v>528</v>
       </c>
-      <c r="B530" t="s">
+      <c r="B530" s="9" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7737,7 +7738,7 @@
       <c r="A531" s="1">
         <v>529</v>
       </c>
-      <c r="B531" t="s">
+      <c r="B531" s="9" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7750,5 +7751,6 @@
     <hyperlink ref="A1" r:id="rId1" xr:uid="{E4BE23F5-8686-4318-92B6-7D7B715CDD5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/AWS-Exam-Certificate-Preparation/SAP-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1237" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{942BFD94-C0E5-4B4E-8359-F2E487A90595}"/>
+  <xr:revisionPtr revIDLastSave="1387" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF428EF-D65D-4AF7-9684-46C7E06EF05C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
@@ -5906,7 +5906,7 @@
       <c r="A302" s="1">
         <v>300</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B302" s="9" t="s">
         <v>377</v>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       <c r="A303" s="1">
         <v>301</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B303" s="9" t="s">
         <v>286</v>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       <c r="A304" s="1">
         <v>302</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B304" s="9" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       <c r="A305" s="1">
         <v>303</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="9" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       <c r="A306" s="1">
         <v>304</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="9" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       <c r="A307" s="1">
         <v>305</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="9" t="s">
         <v>362</v>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       <c r="A308" s="1">
         <v>306</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="9" t="s">
         <v>428</v>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       <c r="A309" s="1">
         <v>307</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="9" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       <c r="A310" s="1">
         <v>308</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="9" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       <c r="A311" s="1">
         <v>309</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       <c r="A312" s="1">
         <v>310</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="9" t="s">
         <v>359</v>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="A313" s="1">
         <v>311</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="9" t="s">
         <v>358</v>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       <c r="A314" s="1">
         <v>312</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="9" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       <c r="A315" s="1">
         <v>313</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="9" t="s">
         <v>150</v>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       <c r="A316" s="1">
         <v>314</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="9" t="s">
         <v>414</v>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       <c r="A317" s="1">
         <v>315</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="9" t="s">
         <v>356</v>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       <c r="A318" s="1">
         <v>316</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="9" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       <c r="A319" s="1">
         <v>317</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="9" t="s">
         <v>387</v>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       <c r="A320" s="1">
         <v>318</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="9" t="s">
         <v>355</v>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       <c r="A321" s="1">
         <v>319</v>
       </c>
-      <c r="B321" t="s">
+      <c r="B321" s="9" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       <c r="A322" s="1">
         <v>320</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B322" s="9" t="s">
         <v>405</v>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       <c r="A323" s="1">
         <v>321</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B323" s="9" t="s">
         <v>200</v>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       <c r="A324" s="1">
         <v>322</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B324" s="9" t="s">
         <v>91</v>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       <c r="A325" s="1">
         <v>323</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B325" s="9" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       <c r="A326" s="1">
         <v>324</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="9" t="s">
         <v>100</v>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       <c r="A327" s="1">
         <v>325</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="9" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       <c r="A328" s="1">
         <v>326</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="9" t="s">
         <v>99</v>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       <c r="A329" s="1">
         <v>327</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="9" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       <c r="A330" s="1">
         <v>328</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       <c r="A331" s="1">
         <v>329</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="9" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       <c r="A332" s="1">
         <v>330</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="9" t="s">
         <v>532</v>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       <c r="A333" s="1">
         <v>331</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="9" t="s">
         <v>478</v>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       <c r="A334" s="1">
         <v>332</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="9" t="s">
         <v>535</v>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       <c r="A335" s="1">
         <v>333</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="9" t="s">
         <v>423</v>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       <c r="A336" s="1">
         <v>334</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="9" t="s">
         <v>513</v>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       <c r="A337" s="1">
         <v>335</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="9" t="s">
         <v>435</v>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       <c r="A338" s="1">
         <v>336</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="9" t="s">
         <v>415</v>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       <c r="A339" s="1">
         <v>337</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="9" t="s">
         <v>440</v>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       <c r="A340" s="1">
         <v>338</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="9" t="s">
         <v>373</v>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       <c r="A341" s="1">
         <v>339</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="9" t="s">
         <v>149</v>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       <c r="A342" s="1">
         <v>340</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="9" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       <c r="A343" s="1">
         <v>341</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="9" t="s">
         <v>482</v>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       <c r="A344" s="1">
         <v>342</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="9" t="s">
         <v>352</v>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       <c r="A345" s="1">
         <v>343</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="9" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       <c r="A346" s="1">
         <v>344</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="9" t="s">
         <v>338</v>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       <c r="A347" s="1">
         <v>345</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="9" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       <c r="A348" s="1">
         <v>346</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="9" t="s">
         <v>402</v>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       <c r="A349" s="1">
         <v>347</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="9" t="s">
         <v>340</v>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       <c r="A350" s="1">
         <v>348</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       <c r="A351" s="1">
         <v>349</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="9" t="s">
         <v>140</v>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="A352" s="1">
         <v>350</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="9" t="s">
         <v>524</v>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="A353" s="1">
         <v>351</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="9" t="s">
         <v>287</v>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       <c r="A354" s="1">
         <v>352</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="9" t="s">
         <v>522</v>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       <c r="A355" s="1">
         <v>353</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="9" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       <c r="A356" s="1">
         <v>354</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="9" t="s">
         <v>321</v>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       <c r="A357" s="1">
         <v>355</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="9" t="s">
         <v>531</v>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="A358" s="1">
         <v>356</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="9" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       <c r="A359" s="1">
         <v>357</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B359" s="9" t="s">
         <v>308</v>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       <c r="A360" s="1">
         <v>358</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B360" s="9" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       <c r="A361" s="1">
         <v>359</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B361" s="9" t="s">
         <v>289</v>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       <c r="A362" s="1">
         <v>360</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B362" s="9" t="s">
         <v>290</v>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="A363" s="1">
         <v>361</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B363" s="9" t="s">
         <v>98</v>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       <c r="A364" s="1">
         <v>362</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="9" t="s">
         <v>142</v>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       <c r="A365" s="1">
         <v>363</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="9" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       <c r="A366" s="1">
         <v>364</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="9" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       <c r="A367" s="1">
         <v>365</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="9" t="s">
         <v>421</v>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       <c r="A368" s="1">
         <v>366</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="9" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       <c r="A369" s="1">
         <v>367</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="9" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       <c r="A370" s="1">
         <v>368</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="9" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       <c r="A371" s="1">
         <v>369</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B371" s="9" t="s">
         <v>351</v>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       <c r="A372" s="1">
         <v>370</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="9" t="s">
         <v>87</v>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       <c r="A373" s="1">
         <v>371</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="9" t="s">
         <v>477</v>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       <c r="A374" s="1">
         <v>372</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="9" t="s">
         <v>476</v>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       <c r="A375" s="1">
         <v>373</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="9" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       <c r="A376" s="1">
         <v>374</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="9" t="s">
         <v>475</v>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       <c r="A377" s="1">
         <v>375</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="9" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       <c r="A378" s="1">
         <v>376</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B378" s="9" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       <c r="A379" s="1">
         <v>377</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B379" s="9" t="s">
         <v>292</v>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       <c r="A380" s="1">
         <v>378</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B380" s="9" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       <c r="A381" s="1">
         <v>379</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B381" s="9" t="s">
         <v>389</v>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       <c r="A382" s="1">
         <v>380</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B382" s="9" t="s">
         <v>129</v>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       <c r="A383" s="1">
         <v>381</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B383" s="9" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       <c r="A384" s="1">
         <v>382</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B384" s="9" t="s">
         <v>473</v>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       <c r="A385" s="1">
         <v>383</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B385" s="9" t="s">
         <v>472</v>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       <c r="A386" s="1">
         <v>384</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B386" s="9" t="s">
         <v>471</v>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       <c r="A387" s="1">
         <v>385</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B387" s="9" t="s">
         <v>470</v>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       <c r="A388" s="1">
         <v>386</v>
       </c>
-      <c r="B388" t="s">
+      <c r="B388" s="9" t="s">
         <v>469</v>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="A389" s="1">
         <v>387</v>
       </c>
-      <c r="B389" t="s">
+      <c r="B389" s="9" t="s">
         <v>529</v>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       <c r="A390" s="1">
         <v>388</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B390" s="9" t="s">
         <v>390</v>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       <c r="A391" s="1">
         <v>389</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B391" s="9" t="s">
         <v>384</v>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="A392" s="1">
         <v>390</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B392" s="9" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       <c r="A393" s="1">
         <v>391</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="9" t="s">
         <v>467</v>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       <c r="A394" s="1">
         <v>392</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B394" s="9" t="s">
         <v>111</v>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       <c r="A395" s="1">
         <v>393</v>
       </c>
-      <c r="B395" t="s">
+      <c r="B395" s="9" t="s">
         <v>466</v>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       <c r="A396" s="1">
         <v>394</v>
       </c>
-      <c r="B396" t="s">
+      <c r="B396" s="9" t="s">
         <v>110</v>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       <c r="A397" s="1">
         <v>395</v>
       </c>
-      <c r="B397" t="s">
+      <c r="B397" s="9" t="s">
         <v>294</v>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       <c r="A398" s="1">
         <v>396</v>
       </c>
-      <c r="B398" t="s">
+      <c r="B398" s="9" t="s">
         <v>420</v>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       <c r="A399" s="1">
         <v>397</v>
       </c>
-      <c r="B399" t="s">
+      <c r="B399" s="9" t="s">
         <v>481</v>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       <c r="A400" s="1">
         <v>398</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B400" s="9" t="s">
         <v>334</v>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       <c r="A401" s="1">
         <v>399</v>
       </c>
-      <c r="B401" t="s">
+      <c r="B401" s="9" t="s">
         <v>406</v>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       <c r="A402" s="1">
         <v>400</v>
       </c>
-      <c r="B402" t="s">
+      <c r="B402" s="9" t="s">
         <v>310</v>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       <c r="A403" s="1">
         <v>401</v>
       </c>
-      <c r="B403" t="s">
+      <c r="B403" s="9" t="s">
         <v>122</v>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="A404" s="1">
         <v>402</v>
       </c>
-      <c r="B404" t="s">
+      <c r="B404" s="9" t="s">
         <v>437</v>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       <c r="A405" s="1">
         <v>403</v>
       </c>
-      <c r="B405" t="s">
+      <c r="B405" s="9" t="s">
         <v>509</v>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       <c r="A406" s="1">
         <v>404</v>
       </c>
-      <c r="B406" t="s">
+      <c r="B406" s="9" t="s">
         <v>296</v>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       <c r="A407" s="1">
         <v>405</v>
       </c>
-      <c r="B407" t="s">
+      <c r="B407" s="9" t="s">
         <v>208</v>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       <c r="A408" s="1">
         <v>406</v>
       </c>
-      <c r="B408" t="s">
+      <c r="B408" s="9" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       <c r="A409" s="1">
         <v>407</v>
       </c>
-      <c r="B409" t="s">
+      <c r="B409" s="9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       <c r="A410" s="1">
         <v>408</v>
       </c>
-      <c r="B410" t="s">
+      <c r="B410" s="9" t="s">
         <v>459</v>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       <c r="A411" s="1">
         <v>409</v>
       </c>
-      <c r="B411" t="s">
+      <c r="B411" s="9" t="s">
         <v>458</v>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       <c r="A412" s="1">
         <v>410</v>
       </c>
-      <c r="B412" t="s">
+      <c r="B412" s="9" t="s">
         <v>147</v>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       <c r="A413" s="1">
         <v>411</v>
       </c>
-      <c r="B413" t="s">
+      <c r="B413" s="9" t="s">
         <v>493</v>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       <c r="A414" s="1">
         <v>412</v>
       </c>
-      <c r="B414" t="s">
+      <c r="B414" s="9" t="s">
         <v>457</v>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       <c r="A415" s="1">
         <v>413</v>
       </c>
-      <c r="B415" t="s">
+      <c r="B415" s="9" t="s">
         <v>461</v>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       <c r="A416" s="1">
         <v>414</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B416" s="9" t="s">
         <v>76</v>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       <c r="A417" s="1">
         <v>415</v>
       </c>
-      <c r="B417" t="s">
+      <c r="B417" s="9" t="s">
         <v>456</v>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       <c r="A418" s="1">
         <v>416</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B418" s="9" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       <c r="A419" s="1">
         <v>417</v>
       </c>
-      <c r="B419" t="s">
+      <c r="B419" s="9" t="s">
         <v>83</v>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       <c r="A420" s="1">
         <v>418</v>
       </c>
-      <c r="B420" t="s">
+      <c r="B420" s="9" t="s">
         <v>455</v>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       <c r="A421" s="1">
         <v>419</v>
       </c>
-      <c r="B421" t="s">
+      <c r="B421" s="9" t="s">
         <v>454</v>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       <c r="A422" s="1">
         <v>420</v>
       </c>
-      <c r="B422" t="s">
+      <c r="B422" s="9" t="s">
         <v>229</v>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       <c r="A423" s="1">
         <v>421</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B423" s="9" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       <c r="A424" s="1">
         <v>422</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="9" t="s">
         <v>453</v>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       <c r="A425" s="1">
         <v>423</v>
       </c>
-      <c r="B425" t="s">
+      <c r="B425" s="9" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       <c r="A426" s="1">
         <v>424</v>
       </c>
-      <c r="B426" t="s">
+      <c r="B426" s="9" t="s">
         <v>452</v>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       <c r="A427" s="1">
         <v>425</v>
       </c>
-      <c r="B427" t="s">
+      <c r="B427" s="9" t="s">
         <v>416</v>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       <c r="A428" s="1">
         <v>426</v>
       </c>
-      <c r="B428" t="s">
+      <c r="B428" s="9" t="s">
         <v>316</v>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       <c r="A429" s="1">
         <v>427</v>
       </c>
-      <c r="B429" t="s">
+      <c r="B429" s="9" t="s">
         <v>412</v>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       <c r="A430" s="1">
         <v>428</v>
       </c>
-      <c r="B430" t="s">
+      <c r="B430" s="9" t="s">
         <v>378</v>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       <c r="A431" s="1">
         <v>429</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B431" s="9" t="s">
         <v>379</v>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="A432" s="1">
         <v>430</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B432" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       <c r="A433" s="1">
         <v>431</v>
       </c>
-      <c r="B433" t="s">
+      <c r="B433" s="9" t="s">
         <v>366</v>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       <c r="A434" s="1">
         <v>432</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B434" s="9" t="s">
         <v>451</v>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       <c r="A435" s="1">
         <v>433</v>
       </c>
-      <c r="B435" t="s">
+      <c r="B435" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="A436" s="1">
         <v>434</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="9" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       <c r="A437" s="1">
         <v>435</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B437" s="9" t="s">
         <v>202</v>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       <c r="A438" s="1">
         <v>436</v>
       </c>
-      <c r="B438" t="s">
+      <c r="B438" s="9" t="s">
         <v>450</v>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       <c r="A439" s="1">
         <v>437</v>
       </c>
-      <c r="B439" t="s">
+      <c r="B439" s="9" t="s">
         <v>449</v>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       <c r="A440" s="1">
         <v>438</v>
       </c>
-      <c r="B440" t="s">
+      <c r="B440" s="9" t="s">
         <v>448</v>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       <c r="A441" s="1">
         <v>439</v>
       </c>
-      <c r="B441" t="s">
+      <c r="B441" s="9" t="s">
         <v>419</v>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       <c r="A442" s="1">
         <v>440</v>
       </c>
-      <c r="B442" t="s">
+      <c r="B442" s="9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       <c r="A443" s="1">
         <v>441</v>
       </c>
-      <c r="B443" t="s">
+      <c r="B443" s="9" t="s">
         <v>271</v>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       <c r="A444" s="1">
         <v>442</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="9" t="s">
         <v>462</v>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       <c r="A445" s="1">
         <v>443</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="9" t="s">
         <v>422</v>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       <c r="A446" s="1">
         <v>444</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B446" s="9" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       <c r="A447" s="1">
         <v>445</v>
       </c>
-      <c r="B447" t="s">
+      <c r="B447" s="9" t="s">
         <v>463</v>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       <c r="A448" s="1">
         <v>446</v>
       </c>
-      <c r="B448" t="s">
+      <c r="B448" s="9" t="s">
         <v>447</v>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       <c r="A449" s="1">
         <v>447</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B449" s="9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       <c r="A450" s="1">
         <v>448</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B450" s="9" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       <c r="A451" s="1">
         <v>449</v>
       </c>
-      <c r="B451" t="s">
+      <c r="B451" s="9" t="s">
         <v>139</v>
       </c>
     </row>

--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/AWS-Exam-Certificate-Preparation/SAP-C03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1387" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF428EF-D65D-4AF7-9684-46C7E06EF05C}"/>
+  <xr:revisionPtr revIDLastSave="1437" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB9551A-E9FE-4EAA-882F-088371B3492D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
@@ -5506,7 +5506,7 @@
       <c r="A252" s="1">
         <v>250</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="9" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       <c r="A253" s="1">
         <v>251</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="9" t="s">
         <v>525</v>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       <c r="A254" s="1">
         <v>252</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="9" t="s">
         <v>143</v>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       <c r="A255" s="1">
         <v>253</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="9" t="s">
         <v>394</v>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       <c r="A256" s="1">
         <v>254</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="9" t="s">
         <v>291</v>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       <c r="A257" s="1">
         <v>255</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="9" t="s">
         <v>167</v>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       <c r="A258" s="1">
         <v>256</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="9" t="s">
         <v>500</v>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       <c r="A259" s="1">
         <v>257</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="9" t="s">
         <v>512</v>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       <c r="A260" s="1">
         <v>258</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="9" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       <c r="A261" s="1">
         <v>259</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="9" t="s">
         <v>369</v>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       <c r="A262" s="1">
         <v>260</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="9" t="s">
         <v>514</v>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       <c r="A263" s="1">
         <v>261</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="9" t="s">
         <v>372</v>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       <c r="A264" s="1">
         <v>262</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="9" t="s">
         <v>479</v>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       <c r="A265" s="1">
         <v>263</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="9" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       <c r="A266" s="1">
         <v>264</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="9" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       <c r="A267" s="1">
         <v>265</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="9" t="s">
         <v>386</v>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       <c r="A268" s="1">
         <v>266</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="9" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       <c r="A269" s="1">
         <v>267</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="9" t="s">
         <v>413</v>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       <c r="A270" s="1">
         <v>268</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="9" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       <c r="A271" s="1">
         <v>269</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="9" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       <c r="A272" s="1">
         <v>270</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="9" t="s">
         <v>221</v>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       <c r="A273" s="1">
         <v>271</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="9" t="s">
         <v>398</v>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="A274" s="1">
         <v>272</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="9" t="s">
         <v>180</v>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       <c r="A275" s="1">
         <v>273</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="9" t="s">
         <v>388</v>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       <c r="A276" s="1">
         <v>274</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="9" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       <c r="A277" s="1">
         <v>275</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="9" t="s">
         <v>498</v>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       <c r="A278" s="1">
         <v>276</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="9" t="s">
         <v>434</v>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       <c r="A279" s="1">
         <v>277</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="9" t="s">
         <v>381</v>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       <c r="A280" s="1">
         <v>278</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="9" t="s">
         <v>363</v>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       <c r="A281" s="1">
         <v>279</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="9" t="s">
         <v>307</v>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       <c r="A282" s="1">
         <v>280</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="9" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       <c r="A283" s="1">
         <v>281</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="9" t="s">
         <v>480</v>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       <c r="A284" s="1">
         <v>282</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="9" t="s">
         <v>499</v>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       <c r="A285" s="1">
         <v>283</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       <c r="A286" s="1">
         <v>284</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="9" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="A287" s="1">
         <v>285</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="9" t="s">
         <v>526</v>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       <c r="A288" s="1">
         <v>286</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="9" t="s">
         <v>534</v>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       <c r="A289" s="1">
         <v>287</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="9" t="s">
         <v>515</v>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       <c r="A290" s="1">
         <v>288</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="9" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       <c r="A291" s="1">
         <v>289</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="9" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       <c r="A292" s="1">
         <v>290</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="9" t="s">
         <v>504</v>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       <c r="A293" s="1">
         <v>291</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="9" t="s">
         <v>527</v>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       <c r="A294" s="1">
         <v>292</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="9" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       <c r="A295" s="1">
         <v>293</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="9" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       <c r="A296" s="1">
         <v>294</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="9" t="s">
         <v>516</v>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
       <c r="A297" s="1">
         <v>295</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="9" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       <c r="A298" s="1">
         <v>296</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="9" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       <c r="A299" s="1">
         <v>297</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="9" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       <c r="A300" s="1">
         <v>298</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       <c r="A301" s="1">
         <v>299</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="9" t="s">
         <v>436</v>
       </c>
     </row>

--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/AWS-Exam-Certificate-Preparation/SAP-C03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MY_DevOps_Journey\AWS-Exam-Certificate-Preparation\SAP-C03\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1437" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB9551A-E9FE-4EAA-882F-088371B3492D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
   <sheets>
     <sheet name="ExamTopics" sheetId="4" state="hidden" r:id="rId1"/>
@@ -1678,7 +1678,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2173,14 +2173,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
   <dimension ref="A1:E241"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="B1" s="6" t="s">
         <v>533</v>
       </c>
@@ -2188,7 +2188,7 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="B2" s="2" t="str">
         <f>TEXT(COUNTIF(B5:B242,"Yes")/COUNTA(B5:B242),"0.00%")</f>
         <v>60.00%</v>
@@ -2206,7 +2206,7 @@
         <v>0.00%</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>2092026</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -2297,1162 +2297,1162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1">
       <c r="A19" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1">
       <c r="A22" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1">
       <c r="A23" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1">
       <c r="A24" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1">
       <c r="A25" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1">
       <c r="A26" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1">
       <c r="A27" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1">
       <c r="A28" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1">
       <c r="A29" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1">
       <c r="A30" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1">
       <c r="A31" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1">
       <c r="A32" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1">
       <c r="A33" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1">
       <c r="A34" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1">
       <c r="A35" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1">
       <c r="A36" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1">
       <c r="A37" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1">
       <c r="A38" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1">
       <c r="A39" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1">
       <c r="A40" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1">
       <c r="A41" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1">
       <c r="A42" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1">
       <c r="A43" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1">
       <c r="A44" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1">
       <c r="A45" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1">
       <c r="A46" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1">
       <c r="A47" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1">
       <c r="A48" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1">
       <c r="A49" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1">
       <c r="A50" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1">
       <c r="A51" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1">
       <c r="A52" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1">
       <c r="A53" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1">
       <c r="A54" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1">
       <c r="A55" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1">
       <c r="A56" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1">
       <c r="A57" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1">
       <c r="A58" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1">
       <c r="A59" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1">
       <c r="A60" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1">
       <c r="A61" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1">
       <c r="A62" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1">
       <c r="A63" s="1">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1">
       <c r="A64" s="1">
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1">
       <c r="A65" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1">
       <c r="A66" s="1">
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1">
       <c r="A67" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1">
       <c r="A68" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1">
       <c r="A69" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1">
       <c r="A70" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1">
       <c r="A71" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1">
       <c r="A72" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1">
       <c r="A73" s="1">
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1">
       <c r="A74" s="1">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1">
       <c r="A75" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1">
       <c r="A76" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1">
       <c r="A77" s="1">
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1">
       <c r="A78" s="1">
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1">
       <c r="A79" s="1">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1">
       <c r="A80" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1">
       <c r="A81" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1">
       <c r="A82" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1">
       <c r="A83" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1">
       <c r="A84" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1">
       <c r="A85" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1">
       <c r="A86" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1">
       <c r="A87" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1">
       <c r="A88" s="1">
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1">
       <c r="A89" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1">
       <c r="A90" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1">
       <c r="A91" s="1">
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1">
       <c r="A92" s="1">
         <v>87</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1">
       <c r="A93" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1">
       <c r="A94" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1">
       <c r="A95" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1">
       <c r="A96" s="1">
         <v>91</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1">
       <c r="A97" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1">
       <c r="A98" s="1">
         <v>93</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1">
       <c r="A99" s="1">
         <v>94</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1">
       <c r="A100" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1">
       <c r="A101" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1">
       <c r="A102" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1">
       <c r="A103" s="1">
         <v>98</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1">
       <c r="A104" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1">
       <c r="A105" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1">
       <c r="A106" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1">
       <c r="A107" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1">
       <c r="A108" s="1">
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1">
       <c r="A109" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1">
       <c r="A110" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1">
       <c r="A111" s="1">
         <v>106</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1">
       <c r="A112" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1">
       <c r="A113" s="1">
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1">
       <c r="A114" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1">
       <c r="A115" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1">
       <c r="A116" s="1">
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1">
       <c r="A117" s="1">
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1">
       <c r="A118" s="1">
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1">
       <c r="A119" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1">
       <c r="A120" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1">
       <c r="A121" s="1">
         <v>116</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1">
       <c r="A122" s="1">
         <v>117</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1">
       <c r="A123" s="1">
         <v>118</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1">
       <c r="A124" s="1">
         <v>119</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1">
       <c r="A125" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1">
       <c r="A126" s="1">
         <v>121</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1">
       <c r="A127" s="1">
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1">
       <c r="A128" s="1">
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1">
       <c r="A129" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1">
       <c r="A130" s="1">
         <v>125</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1">
       <c r="A131" s="1">
         <v>126</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1">
       <c r="A132" s="1">
         <v>127</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1">
       <c r="A133" s="1">
         <v>128</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1">
       <c r="A134" s="1">
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1">
       <c r="A135" s="1">
         <v>130</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1">
       <c r="A136" s="1">
         <v>131</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1">
       <c r="A137" s="1">
         <v>132</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1">
       <c r="A138" s="1">
         <v>133</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1">
       <c r="A139" s="1">
         <v>134</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1">
       <c r="A140" s="1">
         <v>135</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1">
       <c r="A141" s="1">
         <v>136</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1">
       <c r="A142" s="1">
         <v>137</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1">
       <c r="A143" s="1">
         <v>138</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1">
       <c r="A144" s="1">
         <v>139</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1">
       <c r="A145" s="1">
         <v>140</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1">
       <c r="A146" s="1">
         <v>141</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1">
       <c r="A147" s="1">
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1">
       <c r="A148" s="1">
         <v>143</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1">
       <c r="A149" s="1">
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1">
       <c r="A150" s="1">
         <v>145</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1">
       <c r="A151" s="1">
         <v>146</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1">
       <c r="A152" s="1">
         <v>147</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1">
       <c r="A153" s="1">
         <v>148</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1">
       <c r="A154" s="1">
         <v>149</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1">
       <c r="A155" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1">
       <c r="A156" s="1">
         <v>151</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1">
       <c r="A157" s="1">
         <v>152</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:1">
       <c r="A158" s="1">
         <v>153</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:1">
       <c r="A159" s="1">
         <v>154</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:1">
       <c r="A160" s="1">
         <v>155</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:1">
       <c r="A161" s="1">
         <v>156</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:1">
       <c r="A162" s="1">
         <v>157</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:1">
       <c r="A163" s="1">
         <v>158</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:1">
       <c r="A164" s="1">
         <v>159</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:1">
       <c r="A165" s="1">
         <v>160</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:1">
       <c r="A166" s="1">
         <v>161</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:1">
       <c r="A167" s="1">
         <v>162</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:1">
       <c r="A168" s="1">
         <v>163</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:1">
       <c r="A169" s="1">
         <v>164</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:1">
       <c r="A170" s="1">
         <v>165</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:1">
       <c r="A171" s="1">
         <v>166</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:1">
       <c r="A172" s="1">
         <v>167</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:1">
       <c r="A173" s="1">
         <v>168</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:1">
       <c r="A174" s="1">
         <v>169</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:1">
       <c r="A175" s="1">
         <v>170</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:1">
       <c r="A176" s="1">
         <v>171</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:1">
       <c r="A177" s="1">
         <v>172</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:1">
       <c r="A178" s="1">
         <v>173</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:1">
       <c r="A179" s="1">
         <v>174</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:1">
       <c r="A180" s="1">
         <v>175</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:1">
       <c r="A181" s="1">
         <v>176</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:1">
       <c r="A182" s="1">
         <v>177</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:1">
       <c r="A183" s="1">
         <v>178</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:1">
       <c r="A184" s="1">
         <v>179</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:1">
       <c r="A185" s="1">
         <v>180</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:1">
       <c r="A186" s="1">
         <v>181</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:1">
       <c r="A187" s="1">
         <v>182</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:1">
       <c r="A188" s="1">
         <v>183</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:1">
       <c r="A189" s="1">
         <v>184</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:1">
       <c r="A190" s="1">
         <v>185</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:1">
       <c r="A191" s="1">
         <v>186</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:1">
       <c r="A192" s="1">
         <v>187</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:1">
       <c r="A193" s="1">
         <v>188</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:1">
       <c r="A194" s="1">
         <v>189</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:1">
       <c r="A195" s="1">
         <v>190</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:1">
       <c r="A196" s="1">
         <v>191</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:1">
       <c r="A197" s="1">
         <v>192</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:1">
       <c r="A198" s="1">
         <v>193</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:1">
       <c r="A199" s="1">
         <v>194</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:1">
       <c r="A200" s="1">
         <v>195</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:1">
       <c r="A201" s="1">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:1">
       <c r="A202" s="1">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:1">
       <c r="A203" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:1">
       <c r="A204" s="1">
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:1">
       <c r="A205" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:1">
       <c r="A206" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:1">
       <c r="A207" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:1">
       <c r="A208" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1">
       <c r="A209" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1">
       <c r="A210" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1">
       <c r="A211" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1">
       <c r="A212" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1">
       <c r="A213" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1">
       <c r="A214" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1">
       <c r="A215" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1">
       <c r="A216" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1">
       <c r="A217" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1">
       <c r="A218" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1">
       <c r="A219" s="1">
         <v>214</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1">
       <c r="A220" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1">
       <c r="A221" s="1">
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1">
       <c r="A222" s="1">
         <v>217</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1">
       <c r="A223" s="1">
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1">
       <c r="A224" s="1">
         <v>219</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1">
       <c r="A225" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1">
       <c r="A226" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1">
       <c r="A227" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1">
       <c r="A228" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1">
       <c r="A229" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1">
       <c r="A230" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1">
       <c r="A231" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1">
       <c r="A232" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1">
       <c r="A233" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:1">
       <c r="A234" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:1">
       <c r="A235" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:1">
       <c r="A236" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:1">
       <c r="A237" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:1">
       <c r="A238" s="1">
         <v>233</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:1">
       <c r="A239" s="1">
         <v>234</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:1">
       <c r="A240" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:1">
       <c r="A241" s="1">
         <v>236</v>
       </c>
@@ -3482,16 +3482,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E3CCDD-CECD-4B29-8FAC-EFB87C60FE25}">
   <dimension ref="A1:C531"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="108.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="2" bestFit="1" customWidth="1"/>
     <col min="7" max="21" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2">
       <c r="A258" s="1">
         <v>256</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2">
       <c r="A259" s="1">
         <v>257</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2">
       <c r="A263" s="1">
         <v>261</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2">
       <c r="A264" s="1">
         <v>262</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2">
       <c r="A265" s="1">
         <v>263</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2">
       <c r="A268" s="1">
         <v>266</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2">
       <c r="A269" s="1">
         <v>267</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2">
       <c r="A306" s="1">
         <v>304</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2">
       <c r="A307" s="1">
         <v>305</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2">
       <c r="A308" s="1">
         <v>306</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2">
       <c r="A309" s="1">
         <v>307</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2">
       <c r="A310" s="1">
         <v>308</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2">
       <c r="A311" s="1">
         <v>309</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2">
       <c r="A312" s="1">
         <v>310</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2">
       <c r="A313" s="1">
         <v>311</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2">
       <c r="A314" s="1">
         <v>312</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2">
       <c r="A315" s="1">
         <v>313</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2">
       <c r="A316" s="1">
         <v>314</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2">
       <c r="A317" s="1">
         <v>315</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2">
       <c r="A318" s="1">
         <v>316</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2">
       <c r="A319" s="1">
         <v>317</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2">
       <c r="A320" s="1">
         <v>318</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2">
       <c r="A321" s="1">
         <v>319</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2">
       <c r="A322" s="1">
         <v>320</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2">
       <c r="A323" s="1">
         <v>321</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2">
       <c r="A324" s="1">
         <v>322</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2">
       <c r="A325" s="1">
         <v>323</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2">
       <c r="A326" s="1">
         <v>324</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2">
       <c r="A327" s="1">
         <v>325</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2">
       <c r="A328" s="1">
         <v>326</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2">
       <c r="A329" s="1">
         <v>327</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2">
       <c r="A330" s="1">
         <v>328</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2">
       <c r="A331" s="1">
         <v>329</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2">
       <c r="A332" s="1">
         <v>330</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2">
       <c r="A333" s="1">
         <v>331</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2">
       <c r="A334" s="1">
         <v>332</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2">
       <c r="A335" s="1">
         <v>333</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2">
       <c r="A336" s="1">
         <v>334</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2">
       <c r="A337" s="1">
         <v>335</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2">
       <c r="A338" s="1">
         <v>336</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2">
       <c r="A339" s="1">
         <v>337</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2">
       <c r="A340" s="1">
         <v>338</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2">
       <c r="A341" s="1">
         <v>339</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2">
       <c r="A342" s="1">
         <v>340</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2">
       <c r="A343" s="1">
         <v>341</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2">
       <c r="A344" s="1">
         <v>342</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2">
       <c r="A345" s="1">
         <v>343</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2">
       <c r="A346" s="1">
         <v>344</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2">
       <c r="A347" s="1">
         <v>345</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2">
       <c r="A348" s="1">
         <v>346</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2">
       <c r="A349" s="1">
         <v>347</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2">
       <c r="A350" s="1">
         <v>348</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2">
       <c r="A351" s="1">
         <v>349</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2">
       <c r="A352" s="1">
         <v>350</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2">
       <c r="A353" s="1">
         <v>351</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2">
       <c r="A354" s="1">
         <v>352</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2">
       <c r="A355" s="1">
         <v>353</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2">
       <c r="A356" s="1">
         <v>354</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2">
       <c r="A357" s="1">
         <v>355</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2">
       <c r="A358" s="1">
         <v>356</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2">
       <c r="A359" s="1">
         <v>357</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2">
       <c r="A360" s="1">
         <v>358</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2">
       <c r="A361" s="1">
         <v>359</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2">
       <c r="A362" s="1">
         <v>360</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2">
       <c r="A363" s="1">
         <v>361</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2">
       <c r="A364" s="1">
         <v>362</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2">
       <c r="A365" s="1">
         <v>363</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2">
       <c r="A366" s="1">
         <v>364</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2">
       <c r="A367" s="1">
         <v>365</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2">
       <c r="A368" s="1">
         <v>366</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2">
       <c r="A369" s="1">
         <v>367</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2">
       <c r="A370" s="1">
         <v>368</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2">
       <c r="A371" s="1">
         <v>369</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2">
       <c r="A372" s="1">
         <v>370</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2">
       <c r="A373" s="1">
         <v>371</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2">
       <c r="A374" s="1">
         <v>372</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2">
       <c r="A375" s="1">
         <v>373</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2">
       <c r="A376" s="1">
         <v>374</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2">
       <c r="A377" s="1">
         <v>375</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2">
       <c r="A378" s="1">
         <v>376</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2">
       <c r="A379" s="1">
         <v>377</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2">
       <c r="A380" s="1">
         <v>378</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2">
       <c r="A381" s="1">
         <v>379</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2">
       <c r="A382" s="1">
         <v>380</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2">
       <c r="A383" s="1">
         <v>381</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2">
       <c r="A384" s="1">
         <v>382</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2">
       <c r="A385" s="1">
         <v>383</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2">
       <c r="A386" s="1">
         <v>384</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2">
       <c r="A387" s="1">
         <v>385</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2">
       <c r="A388" s="1">
         <v>386</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2">
       <c r="A389" s="1">
         <v>387</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2">
       <c r="A390" s="1">
         <v>388</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2">
       <c r="A391" s="1">
         <v>389</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2">
       <c r="A392" s="1">
         <v>390</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2">
       <c r="A393" s="1">
         <v>391</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2">
       <c r="A394" s="1">
         <v>392</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2">
       <c r="A395" s="1">
         <v>393</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2">
       <c r="A396" s="1">
         <v>394</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2">
       <c r="A397" s="1">
         <v>395</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2">
       <c r="A398" s="1">
         <v>396</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2">
       <c r="A404" s="1">
         <v>402</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2">
       <c r="A406" s="1">
         <v>404</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2">
       <c r="A407" s="1">
         <v>405</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2">
       <c r="A408" s="1">
         <v>406</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2">
       <c r="A409" s="1">
         <v>407</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2">
       <c r="A410" s="1">
         <v>408</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2">
       <c r="A411" s="1">
         <v>409</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2">
       <c r="A412" s="1">
         <v>410</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2">
       <c r="A413" s="1">
         <v>411</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2">
       <c r="A414" s="1">
         <v>412</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2">
       <c r="A415" s="1">
         <v>413</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2">
       <c r="A416" s="1">
         <v>414</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2">
       <c r="A417" s="1">
         <v>415</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2">
       <c r="A418" s="1">
         <v>416</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2">
       <c r="A419" s="1">
         <v>417</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2">
       <c r="A420" s="1">
         <v>418</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2">
       <c r="A421" s="1">
         <v>419</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2">
       <c r="A422" s="1">
         <v>420</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2">
       <c r="A423" s="1">
         <v>421</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2">
       <c r="A424" s="1">
         <v>422</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2">
       <c r="A425" s="1">
         <v>423</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2">
       <c r="A426" s="1">
         <v>424</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2">
       <c r="A427" s="1">
         <v>425</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2">
       <c r="A428" s="1">
         <v>426</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2">
       <c r="A429" s="1">
         <v>427</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2">
       <c r="A430" s="1">
         <v>428</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2">
       <c r="A431" s="1">
         <v>429</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2">
       <c r="A432" s="1">
         <v>430</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2">
       <c r="A433" s="1">
         <v>431</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2">
       <c r="A434" s="1">
         <v>432</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2">
       <c r="A435" s="1">
         <v>433</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2">
       <c r="A436" s="1">
         <v>434</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2">
       <c r="A437" s="1">
         <v>435</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2">
       <c r="A438" s="1">
         <v>436</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2">
       <c r="A439" s="1">
         <v>437</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2">
       <c r="A440" s="1">
         <v>438</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2">
       <c r="A441" s="1">
         <v>439</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2">
       <c r="A442" s="1">
         <v>440</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2">
       <c r="A443" s="1">
         <v>441</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2">
       <c r="A444" s="1">
         <v>442</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2">
       <c r="A445" s="1">
         <v>443</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2">
       <c r="A446" s="1">
         <v>444</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2">
       <c r="A447" s="1">
         <v>445</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2">
       <c r="A448" s="1">
         <v>446</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2">
       <c r="A449" s="1">
         <v>447</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2">
       <c r="A450" s="1">
         <v>448</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2">
       <c r="A451" s="1">
         <v>449</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2">
       <c r="A452" s="1">
         <v>450</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2">
       <c r="A453" s="1">
         <v>451</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2">
       <c r="A454" s="1">
         <v>452</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2">
       <c r="A455" s="1">
         <v>453</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2">
       <c r="A456" s="1">
         <v>454</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2">
       <c r="A457" s="1">
         <v>455</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2">
       <c r="A458" s="1">
         <v>456</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2">
       <c r="A459" s="1">
         <v>457</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2">
       <c r="A460" s="1">
         <v>458</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2">
       <c r="A461" s="1">
         <v>459</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2">
       <c r="A462" s="1">
         <v>460</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2">
       <c r="A463" s="1">
         <v>461</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2">
       <c r="A464" s="1">
         <v>462</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2">
       <c r="A465" s="1">
         <v>463</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2">
       <c r="A466" s="1">
         <v>464</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2">
       <c r="A467" s="1">
         <v>465</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2">
       <c r="A468" s="1">
         <v>466</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2">
       <c r="A469" s="1">
         <v>467</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2">
       <c r="A470" s="1">
         <v>468</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2">
       <c r="A471" s="1">
         <v>469</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2">
       <c r="A472" s="1">
         <v>470</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2">
       <c r="A473" s="1">
         <v>471</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2">
       <c r="A474" s="1">
         <v>472</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2">
       <c r="A475" s="1">
         <v>473</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2">
       <c r="A476" s="1">
         <v>474</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2">
       <c r="A477" s="1">
         <v>475</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2">
       <c r="A478" s="1">
         <v>476</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2">
       <c r="A479" s="1">
         <v>477</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2">
       <c r="A480" s="1">
         <v>478</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2">
       <c r="A481" s="1">
         <v>479</v>
       </c>
@@ -7342,7 +7342,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2">
       <c r="A482" s="1">
         <v>480</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2">
       <c r="A483" s="1">
         <v>481</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2">
       <c r="A484" s="1">
         <v>482</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2">
       <c r="A485" s="1">
         <v>483</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2">
       <c r="A486" s="1">
         <v>484</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2">
       <c r="A487" s="1">
         <v>485</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2">
       <c r="A488" s="1">
         <v>486</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2">
       <c r="A489" s="1">
         <v>487</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2">
       <c r="A490" s="1">
         <v>488</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2">
       <c r="A491" s="1">
         <v>489</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2">
       <c r="A492" s="1">
         <v>490</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2">
       <c r="A493" s="1">
         <v>491</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2">
       <c r="A494" s="1">
         <v>492</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2">
       <c r="A495" s="1">
         <v>493</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2">
       <c r="A496" s="1">
         <v>494</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2">
       <c r="A497" s="1">
         <v>495</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2">
       <c r="A498" s="1">
         <v>496</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2">
       <c r="A499" s="1">
         <v>497</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2">
       <c r="A500" s="1">
         <v>498</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2">
       <c r="A501" s="1">
         <v>499</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2">
       <c r="A502" s="1">
         <v>500</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2">
       <c r="A503" s="1">
         <v>501</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2">
       <c r="A504" s="1">
         <v>502</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2">
       <c r="A505" s="1">
         <v>503</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2">
       <c r="A506" s="1">
         <v>504</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2">
       <c r="A507" s="1">
         <v>505</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2">
       <c r="A508" s="1">
         <v>506</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2">
       <c r="A509" s="1">
         <v>507</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2">
       <c r="A510" s="1">
         <v>508</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2">
       <c r="A511" s="1">
         <v>509</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2">
       <c r="A512" s="1">
         <v>510</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2">
       <c r="A513" s="1">
         <v>511</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2">
       <c r="A514" s="1">
         <v>512</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2">
       <c r="A515" s="1">
         <v>513</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2">
       <c r="A516" s="1">
         <v>514</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2">
       <c r="A517" s="1">
         <v>515</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2">
       <c r="A518" s="1">
         <v>516</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2">
       <c r="A519" s="1">
         <v>517</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2">
       <c r="A520" s="1">
         <v>518</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2">
       <c r="A521" s="1">
         <v>519</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2">
       <c r="A522" s="1">
         <v>520</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2">
       <c r="A523" s="1">
         <v>521</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2">
       <c r="A524" s="1">
         <v>522</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2">
       <c r="A525" s="1">
         <v>523</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2">
       <c r="A526" s="1">
         <v>524</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2">
       <c r="A527" s="1">
         <v>525</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2">
       <c r="A528" s="1">
         <v>526</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2">
       <c r="A529" s="1">
         <v>527</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2">
       <c r="A530" s="1">
         <v>528</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2">
       <c r="A531" s="1">
         <v>529</v>
       </c>

--- a/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
+++ b/SAP-C03/SAP-C02-ExamTopics-Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MY_DevOps_Journey\AWS-Exam-Certificate-Preparation\SAP-C03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1437" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB9551A-E9FE-4EAA-882F-088371B3492D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE935C2-0327-46E3-B737-17454AA36825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
@@ -1759,7 +1759,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1774,18 +1774,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2181,12 +2184,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5">
       <c r="B2" s="2" t="str">
@@ -3484,2026 +3487,2027 @@
   <dimension ref="A1:C531"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="108.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="21" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="2" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="21" width="3" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7265625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="9" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="9" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="9" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="1">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="9" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="9" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1">
+      <c r="A18" s="10">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1">
+      <c r="A19" s="10">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1">
+      <c r="A20" s="10">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="9" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1">
+      <c r="A21" s="10">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1">
+      <c r="A22" s="10">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1">
+      <c r="A23" s="10">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="9" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1">
+      <c r="A24" s="10">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1">
+      <c r="A25" s="10">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="9" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1">
+      <c r="A26" s="10">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="9" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1">
+      <c r="A27" s="10">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1">
+      <c r="A28" s="10">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1">
+      <c r="A29" s="10">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="9" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1">
+      <c r="A30" s="10">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1">
+      <c r="A31" s="10">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1">
+      <c r="A32" s="10">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="9" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1">
+      <c r="A33" s="10">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1">
+      <c r="A34" s="10">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="9" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1">
+      <c r="A35" s="10">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1">
+      <c r="A36" s="10">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="9" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1">
+      <c r="A37" s="10">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1">
+      <c r="A38" s="10">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="9" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1">
+      <c r="A39" s="10">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="9" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1">
+      <c r="A40" s="10">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="9" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1">
+      <c r="A41" s="10">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="9" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1">
+      <c r="A42" s="10">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="9" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1">
+      <c r="A43" s="10">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1">
+      <c r="A44" s="10">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="1">
+      <c r="A45" s="10">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="9" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1">
+      <c r="A46" s="10">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1">
+      <c r="A47" s="10">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="1">
+      <c r="A48" s="10">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="9" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="1">
+      <c r="A49" s="10">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="9" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="1">
+      <c r="A50" s="10">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="9" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1">
+      <c r="A51" s="10">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1">
+      <c r="A52" s="10">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="9" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="1">
+      <c r="A53" s="10">
         <v>51</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="9" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="1">
+      <c r="A54" s="10">
         <v>52</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="9" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="1">
+      <c r="A55" s="10">
         <v>53</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="9" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="1">
+      <c r="A56" s="10">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1">
+      <c r="A57" s="10">
         <v>55</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="9" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1">
+      <c r="A58" s="10">
         <v>56</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="9" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1">
+      <c r="A59" s="10">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="9" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1">
+      <c r="A60" s="10">
         <v>58</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="9" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="1">
+      <c r="A61" s="10">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="9" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="1">
+      <c r="A62" s="10">
         <v>60</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="1">
+      <c r="A63" s="10">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="9" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="1">
+      <c r="A64" s="10">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="9" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="1">
+      <c r="A65" s="10">
         <v>63</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="9" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1">
+      <c r="A66" s="10">
         <v>64</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="9" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="1">
+      <c r="A67" s="10">
         <v>65</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="9" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="1">
+      <c r="A68" s="10">
         <v>66</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="9" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="1">
+      <c r="A69" s="10">
         <v>67</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="1">
+      <c r="A70" s="10">
         <v>68</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="1">
+      <c r="A71" s="10">
         <v>69</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="9" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="1">
+      <c r="A72" s="10">
         <v>70</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="1">
+      <c r="A73" s="10">
         <v>71</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="9" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="1">
+      <c r="A74" s="10">
         <v>72</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="9" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="1">
+      <c r="A75" s="10">
         <v>73</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="9" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="1">
+      <c r="A76" s="10">
         <v>74</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="9" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="1">
+      <c r="A77" s="10">
         <v>75</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="1">
+      <c r="A78" s="10">
         <v>76</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="9" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="1">
+      <c r="A79" s="10">
         <v>77</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="9" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="1">
+      <c r="A80" s="10">
         <v>78</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="9" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="1">
+      <c r="A81" s="10">
         <v>79</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="9" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="1">
+      <c r="A82" s="10">
         <v>80</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="1">
+      <c r="A83" s="10">
         <v>81</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="1">
+      <c r="A84" s="10">
         <v>82</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="9" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="1">
+      <c r="A85" s="10">
         <v>83</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="9" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="1">
+      <c r="A86" s="10">
         <v>84</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="9" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="1">
+      <c r="A87" s="10">
         <v>85</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="9" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="1">
+      <c r="A88" s="10">
         <v>86</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="9" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="1">
+      <c r="A89" s="10">
         <v>87</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="9" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="1">
+      <c r="A90" s="10">
         <v>88</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="9" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="1">
+      <c r="A91" s="10">
         <v>89</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="1">
+      <c r="A92" s="10">
         <v>90</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="1">
+      <c r="A93" s="10">
         <v>91</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="9" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="1">
+      <c r="A94" s="10">
         <v>92</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="9" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="1">
+      <c r="A95" s="10">
         <v>93</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="9" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="1">
+      <c r="A96" s="10">
         <v>94</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="9" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="1">
+      <c r="A97" s="10">
         <v>95</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="9" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="1">
+      <c r="A98" s="10">
         <v>96</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="1">
+      <c r="A99" s="10">
         <v>97</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="9" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="1">
+      <c r="A100" s="10">
         <v>98</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="9" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="1">
+      <c r="A101" s="10">
         <v>99</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="1">
+      <c r="A102" s="10">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="9" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="1">
+      <c r="A103" s="10">
         <v>101</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="1">
+      <c r="A104" s="10">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="1">
+      <c r="A105" s="10">
         <v>103</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="1">
+      <c r="A106" s="10">
         <v>104</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="1">
+      <c r="A107" s="10">
         <v>105</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="1">
+      <c r="A108" s="10">
         <v>106</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="1">
+      <c r="A109" s="10">
         <v>107</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="1">
+      <c r="A110" s="10">
         <v>108</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="1">
+      <c r="A111" s="10">
         <v>109</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="1">
+      <c r="A112" s="10">
         <v>110</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="1">
+      <c r="A113" s="10">
         <v>111</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="1">
+      <c r="A114" s="10">
         <v>112</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="1">
+      <c r="A115" s="10">
         <v>113</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="1">
+      <c r="A116" s="10">
         <v>114</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="1">
+      <c r="A117" s="10">
         <v>115</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="1">
+      <c r="A118" s="10">
         <v>116</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="1">
+      <c r="A119" s="10">
         <v>117</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="1">
+      <c r="A120" s="10">
         <v>118</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="1">
+      <c r="A121" s="10">
         <v>119</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="1">
+      <c r="A122" s="10">
         <v>120</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="1">
+      <c r="A123" s="10">
         <v>121</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="9" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="1">
+      <c r="A124" s="10">
         <v>122</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="9" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="1">
+      <c r="A125" s="10">
         <v>123</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="9" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="1">
+      <c r="A126" s="10">
         <v>124</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="9" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="1">
+      <c r="A127" s="10">
         <v>125</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="9" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="1">
+      <c r="A128" s="10">
         <v>126</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="1">
+      <c r="A129" s="10">
         <v>127</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="9" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="1">
+      <c r="A130" s="10">
         <v>128</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="9" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="1">
+      <c r="A131" s="10">
         <v>129</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="9" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="1">
+      <c r="A132" s="10">
         <v>130</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="9" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="1">
+      <c r="A133" s="10">
         <v>131</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="9" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="1">
+      <c r="A134" s="10">
         <v>132</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="9" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="1">
+      <c r="A135" s="10">
         <v>133</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="9" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="1">
+      <c r="A136" s="10">
         <v>134</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="9" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="1">
+      <c r="A137" s="10">
         <v>135</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="9" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="1">
+      <c r="A138" s="10">
         <v>136</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="1">
+      <c r="A139" s="10">
         <v>137</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="9" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="1">
+      <c r="A140" s="10">
         <v>138</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="1">
+      <c r="A141" s="10">
         <v>139</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="9" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="1">
+      <c r="A142" s="10">
         <v>140</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="9" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="1">
+      <c r="A143" s="10">
         <v>141</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="9" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="1">
+      <c r="A144" s="10">
         <v>142</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="9" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1">
+      <c r="A145" s="10">
         <v>143</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="9" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="1">
+      <c r="A146" s="10">
         <v>144</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="9" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="1">
+      <c r="A147" s="10">
         <v>145</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="1">
+      <c r="A148" s="10">
         <v>146</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="9" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="1">
+      <c r="A149" s="10">
         <v>147</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="9" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="1">
+      <c r="A150" s="10">
         <v>148</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="9" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="1">
+      <c r="A151" s="10">
         <v>149</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="9" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="1">
+      <c r="A152" s="10">
         <v>150</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="9" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="1">
+      <c r="A153" s="10">
         <v>151</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="9" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="1">
+      <c r="A154" s="10">
         <v>152</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="1">
+      <c r="A155" s="10">
         <v>153</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="9" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="1">
+      <c r="A156" s="10">
         <v>154</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="9" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="1">
+      <c r="A157" s="10">
         <v>155</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="9" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="1">
+      <c r="A158" s="10">
         <v>156</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="1">
+      <c r="A159" s="10">
         <v>157</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="9" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="1">
+      <c r="A160" s="10">
         <v>158</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="9" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="1">
+      <c r="A161" s="10">
         <v>159</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="9" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="1">
+      <c r="A162" s="10">
         <v>160</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="9" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="1">
+      <c r="A163" s="10">
         <v>161</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="9" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="1">
+      <c r="A164" s="10">
         <v>162</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="9" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="1">
+      <c r="A165" s="10">
         <v>163</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="9" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="1">
+      <c r="A166" s="10">
         <v>164</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="9" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="1">
+      <c r="A167" s="10">
         <v>165</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="1">
+      <c r="A168" s="10">
         <v>166</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="1">
+      <c r="A169" s="10">
         <v>167</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="9" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="1">
+      <c r="A170" s="10">
         <v>168</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="1">
+      <c r="A171" s="10">
         <v>169</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="9" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="1">
+      <c r="A172" s="10">
         <v>170</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="9" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="1">
+      <c r="A173" s="10">
         <v>171</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="9" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="1">
+      <c r="A174" s="10">
         <v>172</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="9" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="1">
+      <c r="A175" s="10">
         <v>173</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="1">
+      <c r="A176" s="10">
         <v>174</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="9" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="1">
+      <c r="A177" s="10">
         <v>175</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="9" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="1">
+      <c r="A178" s="10">
         <v>176</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="9" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="1">
+      <c r="A179" s="10">
         <v>177</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="1">
+      <c r="A180" s="10">
         <v>178</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="9" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="1">
+      <c r="A181" s="10">
         <v>179</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="9" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="1">
+      <c r="A182" s="10">
         <v>180</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="1">
+      <c r="A183" s="10">
         <v>181</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="1">
+      <c r="A184" s="10">
         <v>182</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="9" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="1">
+      <c r="A185" s="10">
         <v>183</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="1">
+      <c r="A186" s="10">
         <v>184</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="1">
+      <c r="A187" s="10">
         <v>185</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="1">
+      <c r="A188" s="10">
         <v>186</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="9" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="1">
+      <c r="A189" s="10">
         <v>187</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="9" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="1">
+      <c r="A190" s="10">
         <v>188</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="9" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="1">
+      <c r="A191" s="10">
         <v>189</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="1">
+      <c r="A192" s="10">
         <v>190</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="9" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="1">
+      <c r="A193" s="10">
         <v>191</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="9" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="1">
+      <c r="A194" s="10">
         <v>192</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="9" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="1">
+      <c r="A195" s="10">
         <v>193</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="1">
+      <c r="A196" s="10">
         <v>194</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="1">
+      <c r="A197" s="10">
         <v>195</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="9" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="1">
+      <c r="A198" s="10">
         <v>196</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="9" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="1">
+      <c r="A199" s="10">
         <v>197</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="9" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="1">
+      <c r="A200" s="10">
         <v>198</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="1">
+      <c r="A201" s="10">
         <v>199</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="9" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="1">
+      <c r="A202" s="10">
         <v>200</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="9" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="1">
+      <c r="A203" s="10">
         <v>201</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="9" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="1">
+      <c r="A204" s="10">
         <v>202</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="9" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="1">
+      <c r="A205" s="10">
         <v>203</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="9" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="1">
+      <c r="A206" s="10">
         <v>204</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="9" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="1">
+      <c r="A207" s="10">
         <v>205</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="1">
+      <c r="A208" s="10">
         <v>206</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="1">
+      <c r="A209" s="10">
         <v>207</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="1">
+      <c r="A210" s="10">
         <v>208</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="1">
+      <c r="A211" s="10">
         <v>209</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="9" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="1">
+      <c r="A212" s="10">
         <v>210</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="1">
+      <c r="A213" s="10">
         <v>211</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="9" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="1">
+      <c r="A214" s="10">
         <v>212</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="9" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="1">
+      <c r="A215" s="10">
         <v>213</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="9" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="1">
+      <c r="A216" s="10">
         <v>214</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="9" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="1">
+      <c r="A217" s="10">
         <v>215</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="1">
+      <c r="A218" s="10">
         <v>216</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="1">
+      <c r="A219" s="10">
         <v>217</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="9" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="1">
+      <c r="A220" s="10">
         <v>218</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="1">
+      <c r="A221" s="10">
         <v>219</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="9" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="1">
+      <c r="A222" s="10">
         <v>220</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="9" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="1">
+      <c r="A223" s="10">
         <v>221</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="9" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="1">
+      <c r="A224" s="10">
         <v>222</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="1">
+      <c r="A225" s="10">
         <v>223</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="9" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="1">
+      <c r="A226" s="10">
         <v>224</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="9" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="1">
+      <c r="A227" s="10">
         <v>225</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="9" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="1">
+      <c r="A228" s="10">
         <v>226</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="9" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="1">
+      <c r="A229" s="10">
         <v>227</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="9" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="1">
+      <c r="A230" s="10">
         <v>228</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="1">
+      <c r="A231" s="10">
         <v>229</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="9" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="1">
+      <c r="A232" s="10">
         <v>230</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="1">
+      <c r="A233" s="10">
         <v>231</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="9" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="1">
+      <c r="A234" s="10">
         <v>232</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="9" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="1">
+      <c r="A235" s="10">
         <v>233</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="9" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="1">
+      <c r="A236" s="10">
         <v>234</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="9" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="1">
+      <c r="A237" s="10">
         <v>235</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="9" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="1">
+      <c r="A238" s="10">
         <v>236</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="9" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="1">
+      <c r="A239" s="10">
         <v>237</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="9" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="1">
+      <c r="A240" s="10">
         <v>238</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="9" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="1">
+      <c r="A241" s="10">
         <v>239</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="9" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="1">
+      <c r="A242" s="10">
         <v>240</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="9" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="1">
+      <c r="A243" s="10">
         <v>241</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="9" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="1">
+      <c r="A244" s="10">
         <v>242</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="9" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="1">
+      <c r="A245" s="10">
         <v>243</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="9" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="1">
+      <c r="A246" s="10">
         <v>244</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="9" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="1">
+      <c r="A247" s="10">
         <v>245</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="1">
+      <c r="A248" s="10">
         <v>246</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="9" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="1">
+      <c r="A249" s="10">
         <v>247</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="9" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="1">
+      <c r="A250" s="10">
         <v>248</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="9" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="1">
+      <c r="A251" s="10">
         <v>249</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="9" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="1">
+      <c r="A252" s="10">
         <v>250</v>
       </c>
       <c r="B252" s="9" t="s">
@@ -5511,7 +5515,7 @@
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="1">
+      <c r="A253" s="10">
         <v>251</v>
       </c>
       <c r="B253" s="9" t="s">
@@ -5519,7 +5523,7 @@
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="1">
+      <c r="A254" s="10">
         <v>252</v>
       </c>
       <c r="B254" s="9" t="s">
@@ -5527,7 +5531,7 @@
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="1">
+      <c r="A255" s="10">
         <v>253</v>
       </c>
       <c r="B255" s="9" t="s">
@@ -5535,7 +5539,7 @@
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="1">
+      <c r="A256" s="10">
         <v>254</v>
       </c>
       <c r="B256" s="9" t="s">
@@ -5543,7 +5547,7 @@
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="1">
+      <c r="A257" s="10">
         <v>255</v>
       </c>
       <c r="B257" s="9" t="s">
@@ -5551,7 +5555,7 @@
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="1">
+      <c r="A258" s="10">
         <v>256</v>
       </c>
       <c r="B258" s="9" t="s">
@@ -5559,7 +5563,7 @@
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="1">
+      <c r="A259" s="10">
         <v>257</v>
       </c>
       <c r="B259" s="9" t="s">
@@ -5567,7 +5571,7 @@
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="1">
+      <c r="A260" s="10">
         <v>258</v>
       </c>
       <c r="B260" s="9" t="s">
@@ -5575,7 +5579,7 @@
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="1">
+      <c r="A261" s="10">
         <v>259</v>
       </c>
       <c r="B261" s="9" t="s">
@@ -5583,7 +5587,7 @@
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="1">
+      <c r="A262" s="10">
         <v>260</v>
       </c>
       <c r="B262" s="9" t="s">
@@ -5591,7 +5595,7 @@
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="1">
+      <c r="A263" s="10">
         <v>261</v>
       </c>
       <c r="B263" s="9" t="s">
@@ -5599,7 +5603,7 @@
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="1">
+      <c r="A264" s="10">
         <v>262</v>
       </c>
       <c r="B264" s="9" t="s">
@@ -5607,7 +5611,7 @@
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="1">
+      <c r="A265" s="10">
         <v>263</v>
       </c>
       <c r="B265" s="9" t="s">
@@ -5615,7 +5619,7 @@
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="1">
+      <c r="A266" s="10">
         <v>264</v>
       </c>
       <c r="B266" s="9" t="s">
@@ -5623,7 +5627,7 @@
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="1">
+      <c r="A267" s="10">
         <v>265</v>
       </c>
       <c r="B267" s="9" t="s">
@@ -5631,7 +5635,7 @@
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="1">
+      <c r="A268" s="10">
         <v>266</v>
       </c>
       <c r="B268" s="9" t="s">
@@ -5639,7 +5643,7 @@
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="1">
+      <c r="A269" s="10">
         <v>267</v>
       </c>
       <c r="B269" s="9" t="s">
@@ -5647,7 +5651,7 @@
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="1">
+      <c r="A270" s="10">
         <v>268</v>
       </c>
       <c r="B270" s="9" t="s">
@@ -5655,7 +5659,7 @@
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="1">
+      <c r="A271" s="10">
         <v>269</v>
       </c>
       <c r="B271" s="9" t="s">
@@ -5663,7 +5667,7 @@
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="1">
+      <c r="A272" s="10">
         <v>270</v>
       </c>
       <c r="B272" s="9" t="s">
@@ -5671,7 +5675,7 @@
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="1">
+      <c r="A273" s="10">
         <v>271</v>
       </c>
       <c r="B273" s="9" t="s">
@@ -5679,7 +5683,7 @@
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="1">
+      <c r="A274" s="10">
         <v>272</v>
       </c>
       <c r="B274" s="9" t="s">
@@ -5687,7 +5691,7 @@
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="1">
+      <c r="A275" s="10">
         <v>273</v>
       </c>
       <c r="B275" s="9" t="s">
@@ -5695,7 +5699,7 @@
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="1">
+      <c r="A276" s="10">
         <v>274</v>
       </c>
       <c r="B276" s="9" t="s">
@@ -5703,7 +5707,7 @@
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="1">
+      <c r="A277" s="10">
         <v>275</v>
       </c>
       <c r="B277" s="9" t="s">
@@ -5711,7 +5715,7 @@
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="1">
+      <c r="A278" s="10">
         <v>276</v>
       </c>
       <c r="B278" s="9" t="s">
@@ -5719,7 +5723,7 @@
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="1">
+      <c r="A279" s="10">
         <v>277</v>
       </c>
       <c r="B279" s="9" t="s">
@@ -5727,7 +5731,7 @@
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="1">
+      <c r="A280" s="10">
         <v>278</v>
       </c>
       <c r="B280" s="9" t="s">
@@ -5735,7 +5739,7 @@
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="1">
+      <c r="A281" s="10">
         <v>279</v>
       </c>
       <c r="B281" s="9" t="s">
@@ -5743,7 +5747,7 @@
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="1">
+      <c r="A282" s="10">
         <v>280</v>
       </c>
       <c r="B282" s="9" t="s">
@@ -5751,7 +5755,7 @@
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="1">
+      <c r="A283" s="10">
         <v>281</v>
       </c>
       <c r="B283" s="9" t="s">
@@ -5759,7 +5763,7 @@
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="1">
+      <c r="A284" s="10">
         <v>282</v>
       </c>
       <c r="B284" s="9" t="s">
@@ -5767,7 +5771,7 @@
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="1">
+      <c r="A285" s="10">
         <v>283</v>
       </c>
       <c r="B285" s="9" t="s">
@@ -5775,7 +5779,7 @@
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="1">
+      <c r="A286" s="10">
         <v>284</v>
       </c>
       <c r="B286" s="9" t="s">
@@ -5783,7 +5787,7 @@
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="1">
+      <c r="A287" s="10">
         <v>285</v>
       </c>
       <c r="B287" s="9" t="s">
@@ -5791,7 +5795,7 @@
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="1">
+      <c r="A288" s="10">
         <v>286</v>
       </c>
       <c r="B288" s="9" t="s">
@@ -5799,7 +5803,7 @@
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="1">
+      <c r="A289" s="10">
         <v>287</v>
       </c>
       <c r="B289" s="9" t="s">
@@ -5807,7 +5811,7 @@
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="1">
+      <c r="A290" s="10">
         <v>288</v>
       </c>
       <c r="B290" s="9" t="s">
@@ -5815,7 +5819,7 @@
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="1">
+      <c r="A291" s="10">
         <v>289</v>
       </c>
       <c r="B291" s="9" t="s">
@@ -5823,7 +5827,7 @@
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="1">
+      <c r="A292" s="10">
         <v>290</v>
       </c>
       <c r="B292" s="9" t="s">
@@ -5831,7 +5835,7 @@
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="1">
+      <c r="A293" s="10">
         <v>291</v>
       </c>
       <c r="B293" s="9" t="s">
@@ -5839,7 +5843,7 @@
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="1">
+      <c r="A294" s="10">
         <v>292</v>
       </c>
       <c r="B294" s="9" t="s">
@@ -5847,7 +5851,7 @@
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="1">
+      <c r="A295" s="10">
         <v>293</v>
       </c>
       <c r="B295" s="9" t="s">
@@ -5855,7 +5859,7 @@
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="1">
+      <c r="A296" s="10">
         <v>294</v>
       </c>
       <c r="B296" s="9" t="s">
@@ -5863,7 +5867,7 @@
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="1">
+      <c r="A297" s="10">
         <v>295</v>
       </c>
       <c r="B297" s="9" t="s">
@@ -5871,7 +5875,7 @@
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="1">
+      <c r="A298" s="10">
         <v>296</v>
       </c>
       <c r="B298" s="9" t="s">
@@ -5879,7 +5883,7 @@
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="1">
+      <c r="A299" s="10">
         <v>297</v>
       </c>
       <c r="B299" s="9" t="s">
@@ -5887,7 +5891,7 @@
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="1">
+      <c r="A300" s="10">
         <v>298</v>
       </c>
       <c r="B300" s="9" t="s">
@@ -5895,7 +5899,7 @@
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="1">
+      <c r="A301" s="10">
         <v>299</v>
       </c>
       <c r="B301" s="9" t="s">
@@ -5903,7 +5907,7 @@
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="1">
+      <c r="A302" s="10">
         <v>300</v>
       </c>
       <c r="B302" s="9" t="s">
@@ -5911,7 +5915,7 @@
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="1">
+      <c r="A303" s="10">
         <v>301</v>
       </c>
       <c r="B303" s="9" t="s">
@@ -5919,7 +5923,7 @@
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="1">
+      <c r="A304" s="10">
         <v>302</v>
       </c>
       <c r="B304" s="9" t="s">
@@ -5927,7 +5931,7 @@
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="1">
+      <c r="A305" s="10">
         <v>303</v>
       </c>
       <c r="B305" s="9" t="s">
@@ -5935,7 +5939,7 @@
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="1">
+      <c r="A306" s="10">
         <v>304</v>
       </c>
       <c r="B306" s="9" t="s">
@@ -5943,7 +5947,7 @@
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="1">
+      <c r="A307" s="10">
         <v>305</v>
       </c>
       <c r="B307" s="9" t="s">
@@ -5951,7 +5955,7 @@
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="1">
+      <c r="A308" s="10">
         <v>306</v>
       </c>
       <c r="B308" s="9" t="s">
@@ -5959,7 +5963,7 @@
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="1">
+      <c r="A309" s="10">
         <v>307</v>
       </c>
       <c r="B309" s="9" t="s">
@@ -5967,7 +5971,7 @@
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="1">
+      <c r="A310" s="10">
         <v>308</v>
       </c>
       <c r="B310" s="9" t="s">
@@ -5975,7 +5979,7 @@
       </c>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="1">
+      <c r="A311" s="10">
         <v>309</v>
       </c>
       <c r="B311" s="9" t="s">
@@ -5983,7 +5987,7 @@
       </c>
     </row>
     <row r="312" spans="1:2">
-      <c r="A312" s="1">
+      <c r="A312" s="10">
         <v>310</v>
       </c>
       <c r="B312" s="9" t="s">
@@ -5991,7 +5995,7 @@
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="1">
+      <c r="A313" s="10">
         <v>311</v>
       </c>
       <c r="B313" s="9" t="s">
@@ -5999,7 +6003,7 @@
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="1">
+      <c r="A314" s="10">
         <v>312</v>
       </c>
       <c r="B314" s="9" t="s">
@@ -6007,7 +6011,7 @@
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="1">
+      <c r="A315" s="10">
         <v>313</v>
       </c>
       <c r="B315" s="9" t="s">
@@ -6015,7 +6019,7 @@
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="1">
+      <c r="A316" s="10">
         <v>314</v>
       </c>
       <c r="B316" s="9" t="s">
@@ -6023,7 +6027,7 @@
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="1">
+      <c r="A317" s="10">
         <v>315</v>
       </c>
       <c r="B317" s="9" t="s">
@@ -6031,7 +6035,7 @@
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="1">
+      <c r="A318" s="10">
         <v>316</v>
       </c>
       <c r="B318" s="9" t="s">
@@ -6039,7 +6043,7 @@
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="1">
+      <c r="A319" s="10">
         <v>317</v>
       </c>
       <c r="B319" s="9" t="s">
@@ -6047,7 +6051,7 @@
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="1">
+      <c r="A320" s="10">
         <v>318</v>
       </c>
       <c r="B320" s="9" t="s">
@@ -6055,7 +6059,7 @@
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="1">
+      <c r="A321" s="10">
         <v>319</v>
       </c>
       <c r="B321" s="9" t="s">
@@ -6063,7 +6067,7 @@
       </c>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="1">
+      <c r="A322" s="10">
         <v>320</v>
       </c>
       <c r="B322" s="9" t="s">
@@ -6071,7 +6075,7 @@
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="1">
+      <c r="A323" s="10">
         <v>321</v>
       </c>
       <c r="B323" s="9" t="s">
@@ -6079,7 +6083,7 @@
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="1">
+      <c r="A324" s="10">
         <v>322</v>
       </c>
       <c r="B324" s="9" t="s">
@@ -6087,7 +6091,7 @@
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="1">
+      <c r="A325" s="10">
         <v>323</v>
       </c>
       <c r="B325" s="9" t="s">
@@ -6095,7 +6099,7 @@
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="1">
+      <c r="A326" s="10">
         <v>324</v>
       </c>
       <c r="B326" s="9" t="s">
@@ -6103,7 +6107,7 @@
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="1">
+      <c r="A327" s="10">
         <v>325</v>
       </c>
       <c r="B327" s="9" t="s">
@@ -6111,7 +6115,7 @@
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="1">
+      <c r="A328" s="10">
         <v>326</v>
       </c>
       <c r="B328" s="9" t="s">
@@ -6119,7 +6123,7 @@
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="1">
+      <c r="A329" s="10">
         <v>327</v>
       </c>
       <c r="B329" s="9" t="s">
@@ -6127,7 +6131,7 @@
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="1">
+      <c r="A330" s="10">
         <v>328</v>
       </c>
       <c r="B330" s="9" t="s">
@@ -6135,7 +6139,7 @@
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="1">
+      <c r="A331" s="10">
         <v>329</v>
       </c>
       <c r="B331" s="9" t="s">
@@ -6143,7 +6147,7 @@
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="1">
+      <c r="A332" s="10">
         <v>330</v>
       </c>
       <c r="B332" s="9" t="s">
@@ -6151,7 +6155,7 @@
       </c>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="1">
+      <c r="A333" s="10">
         <v>331</v>
       </c>
       <c r="B333" s="9" t="s">
@@ -6159,7 +6163,7 @@
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="1">
+      <c r="A334" s="10">
         <v>332</v>
       </c>
       <c r="B334" s="9" t="s">
@@ -6167,7 +6171,7 @@
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="1">
+      <c r="A335" s="10">
         <v>333</v>
       </c>
       <c r="B335" s="9" t="s">
@@ -6175,7 +6179,7 @@
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="1">
+      <c r="A336" s="10">
         <v>334</v>
       </c>
       <c r="B336" s="9" t="s">
@@ -6183,7 +6187,7 @@
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="1">
+      <c r="A337" s="10">
         <v>335</v>
       </c>
       <c r="B337" s="9" t="s">
@@ -6191,7 +6195,7 @@
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="1">
+      <c r="A338" s="10">
         <v>336</v>
       </c>
       <c r="B338" s="9" t="s">
@@ -6199,7 +6203,7 @@
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="1">
+      <c r="A339" s="10">
         <v>337</v>
       </c>
       <c r="B339" s="9" t="s">
@@ -6207,7 +6211,7 @@
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="1">
+      <c r="A340" s="10">
         <v>338</v>
       </c>
       <c r="B340" s="9" t="s">
@@ -6215,7 +6219,7 @@
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="1">
+      <c r="A341" s="10">
         <v>339</v>
       </c>
       <c r="B341" s="9" t="s">
@@ -6223,7 +6227,7 @@
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="1">
+      <c r="A342" s="10">
         <v>340</v>
       </c>
       <c r="B342" s="9" t="s">
@@ -6231,7 +6235,7 @@
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="1">
+      <c r="A343" s="10">
         <v>341</v>
       </c>
       <c r="B343" s="9" t="s">
@@ -6239,7 +6243,7 @@
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="1">
+      <c r="A344" s="10">
         <v>342</v>
       </c>
       <c r="B344" s="9" t="s">
@@ -6247,7 +6251,7 @@
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="1">
+      <c r="A345" s="10">
         <v>343</v>
       </c>
       <c r="B345" s="9" t="s">
@@ -6255,7 +6259,7 @@
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="1">
+      <c r="A346" s="10">
         <v>344</v>
       </c>
       <c r="B346" s="9" t="s">
@@ -6263,7 +6267,7 @@
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="1">
+      <c r="A347" s="10">
         <v>345</v>
       </c>
       <c r="B347" s="9" t="s">
@@ -6271,7 +6275,7 @@
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="1">
+      <c r="A348" s="10">
         <v>346</v>
       </c>
       <c r="B348" s="9" t="s">
@@ -6279,7 +6283,7 @@
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="1">
+      <c r="A349" s="10">
         <v>347</v>
       </c>
       <c r="B349" s="9" t="s">
@@ -6287,7 +6291,7 @@
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="1">
+      <c r="A350" s="10">
         <v>348</v>
       </c>
       <c r="B350" s="9" t="s">
@@ -6295,7 +6299,7 @@
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="1">
+      <c r="A351" s="10">
         <v>349</v>
       </c>
       <c r="B351" s="9" t="s">
@@ -6303,7 +6307,7 @@
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="1">
+      <c r="A352" s="10">
         <v>350</v>
       </c>
       <c r="B352" s="9" t="s">
@@ -6311,7 +6315,7 @@
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="1">
+      <c r="A353" s="10">
         <v>351</v>
       </c>
       <c r="B353" s="9" t="s">
@@ -6319,7 +6323,7 @@
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="1">
+      <c r="A354" s="10">
         <v>352</v>
       </c>
       <c r="B354" s="9" t="s">
@@ -6327,7 +6331,7 @@
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="1">
+      <c r="A355" s="10">
         <v>353</v>
       </c>
       <c r="B355" s="9" t="s">
@@ -6335,7 +6339,7 @@
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="1">
+      <c r="A356" s="10">
         <v>354</v>
       </c>
       <c r="B356" s="9" t="s">
@@ -6343,7 +6347,7 @@
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="1">
+      <c r="A357" s="10">
         <v>355</v>
       </c>
       <c r="B357" s="9" t="s">
@@ -6351,7 +6355,7 @@
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="1">
+      <c r="A358" s="10">
         <v>356</v>
       </c>
       <c r="B358" s="9" t="s">
@@ -6359,7 +6363,7 @@
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="1">
+      <c r="A359" s="10">
         <v>357</v>
       </c>
       <c r="B359" s="9" t="s">
@@ -6367,7 +6371,7 @@
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="1">
+      <c r="A360" s="10">
         <v>358</v>
       </c>
       <c r="B360" s="9" t="s">
@@ -6375,7 +6379,7 @@
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="1">
+      <c r="A361" s="10">
         <v>359</v>
       </c>
       <c r="B361" s="9" t="s">
@@ -6383,7 +6387,7 @@
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="1">
+      <c r="A362" s="10">
         <v>360</v>
       </c>
       <c r="B362" s="9" t="s">
@@ -6391,7 +6395,7 @@
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="1">
+      <c r="A363" s="10">
         <v>361</v>
       </c>
       <c r="B363" s="9" t="s">
@@ -6399,7 +6403,7 @@
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="1">
+      <c r="A364" s="10">
         <v>362</v>
       </c>
       <c r="B364" s="9" t="s">
@@ -6407,7 +6411,7 @@
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="1">
+      <c r="A365" s="10">
         <v>363</v>
       </c>
       <c r="B365" s="9" t="s">
@@ -6415,7 +6419,7 @@
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="1">
+      <c r="A366" s="10">
         <v>364</v>
       </c>
       <c r="B366" s="9" t="s">
@@ -6423,7 +6427,7 @@
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="1">
+      <c r="A367" s="10">
         <v>365</v>
       </c>
       <c r="B367" s="9" t="s">
@@ -6431,7 +6435,7 @@
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="1">
+      <c r="A368" s="10">
         <v>366</v>
       </c>
       <c r="B368" s="9" t="s">
@@ -6439,7 +6443,7 @@
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="1">
+      <c r="A369" s="10">
         <v>367</v>
       </c>
       <c r="B369" s="9" t="s">
@@ -6447,7 +6451,7 @@
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="1">
+      <c r="A370" s="10">
         <v>368</v>
       </c>
       <c r="B370" s="9" t="s">
@@ -6455,7 +6459,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="1">
+      <c r="A371" s="10">
         <v>369</v>
       </c>
       <c r="B371" s="9" t="s">
@@ -6463,7 +6467,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="1">
+      <c r="A372" s="10">
         <v>370</v>
       </c>
       <c r="B372" s="9" t="s">
@@ -6471,7 +6475,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="1">
+      <c r="A373" s="10">
         <v>371</v>
       </c>
       <c r="B373" s="9" t="s">
@@ -6479,7 +6483,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="1">
+      <c r="A374" s="10">
         <v>372</v>
       </c>
       <c r="B374" s="9" t="s">
@@ -6487,7 +6491,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="1">
+      <c r="A375" s="10">
         <v>373</v>
       </c>
       <c r="B375" s="9" t="s">
@@ -6495,7 +6499,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="1">
+      <c r="A376" s="10">
         <v>374</v>
       </c>
       <c r="B376" s="9" t="s">
@@ -6503,7 +6507,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="1">
+      <c r="A377" s="10">
         <v>375</v>
       </c>
       <c r="B377" s="9" t="s">
@@ -6511,7 +6515,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="1">
+      <c r="A378" s="10">
         <v>376</v>
       </c>
       <c r="B378" s="9" t="s">
@@ -6519,7 +6523,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="1">
+      <c r="A379" s="10">
         <v>377</v>
       </c>
       <c r="B379" s="9" t="s">
@@ -6527,7 +6531,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="1">
+      <c r="A380" s="10">
         <v>378</v>
       </c>
       <c r="B380" s="9" t="s">
@@ -6535,7 +6539,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="1">
+      <c r="A381" s="10">
         <v>379</v>
       </c>
       <c r="B381" s="9" t="s">
@@ -6543,7 +6547,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="1">
+      <c r="A382" s="10">
         <v>380</v>
       </c>
       <c r="B382" s="9" t="s">
@@ -6551,7 +6555,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="1">
+      <c r="A383" s="10">
         <v>381</v>
       </c>
       <c r="B383" s="9" t="s">
@@ -6559,7 +6563,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="1">
+      <c r="A384" s="10">
         <v>382</v>
       </c>
       <c r="B384" s="9" t="s">
@@ -6567,7 +6571,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="1">
+      <c r="A385" s="10">
         <v>383</v>
       </c>
       <c r="B385" s="9" t="s">
@@ -6575,7 +6579,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="1">
+      <c r="A386" s="10">
         <v>384</v>
       </c>
       <c r="B386" s="9" t="s">
@@ -6583,7 +6587,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="1">
+      <c r="A387" s="10">
         <v>385</v>
       </c>
       <c r="B387" s="9" t="s">
@@ -6591,7 +6595,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="1">
+      <c r="A388" s="10">
         <v>386</v>
       </c>
       <c r="B388" s="9" t="s">
@@ -6599,7 +6603,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="1">
+      <c r="A389" s="10">
         <v>387</v>
       </c>
       <c r="B389" s="9" t="s">
@@ -6607,7 +6611,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="1">
+      <c r="A390" s="10">
         <v>388</v>
       </c>
       <c r="B390" s="9" t="s">
@@ -6615,7 +6619,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="1">
+      <c r="A391" s="10">
         <v>389</v>
       </c>
       <c r="B391" s="9" t="s">
@@ -6623,7 +6627,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="1">
+      <c r="A392" s="10">
         <v>390</v>
       </c>
       <c r="B392" s="9" t="s">
@@ -6631,7 +6635,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="1">
+      <c r="A393" s="10">
         <v>391</v>
       </c>
       <c r="B393" s="9" t="s">
@@ -6639,7 +6643,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="1">
+      <c r="A394" s="10">
         <v>392</v>
       </c>
       <c r="B394" s="9" t="s">
@@ -6647,7 +6651,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="1">
+      <c r="A395" s="10">
         <v>393</v>
       </c>
       <c r="B395" s="9" t="s">
@@ -6655,7 +6659,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="1">
+      <c r="A396" s="10">
         <v>394</v>
       </c>
       <c r="B396" s="9" t="s">
@@ -6663,7 +6667,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="1">
+      <c r="A397" s="10">
         <v>395</v>
       </c>
       <c r="B397" s="9" t="s">
@@ -6671,7 +6675,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="1">
+      <c r="A398" s="10">
         <v>396</v>
       </c>
       <c r="B398" s="9" t="s">
@@ -6679,7 +6683,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="1">
+      <c r="A399" s="10">
         <v>397</v>
       </c>
       <c r="B399" s="9" t="s">
@@ -6687,7 +6691,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="1">
+      <c r="A400" s="10">
         <v>398</v>
       </c>
       <c r="B400" s="9" t="s">
@@ -6695,7 +6699,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="1">
+      <c r="A401" s="10">
         <v>399</v>
       </c>
       <c r="B401" s="9" t="s">
@@ -6703,7 +6707,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="1">
+      <c r="A402" s="10">
         <v>400</v>
       </c>
       <c r="B402" s="9" t="s">
@@ -6711,7 +6715,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="1">
+      <c r="A403" s="10">
         <v>401</v>
       </c>
       <c r="B403" s="9" t="s">
@@ -6719,7 +6723,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="1">
+      <c r="A404" s="10">
         <v>402</v>
       </c>
       <c r="B404" s="9" t="s">
@@ -6727,7 +6731,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="1">
+      <c r="A405" s="10">
         <v>403</v>
       </c>
       <c r="B405" s="9" t="s">
@@ -6735,7 +6739,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="1">
+      <c r="A406" s="10">
         <v>404</v>
       </c>
       <c r="B406" s="9" t="s">
@@ -6743,7 +6747,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="1">
+      <c r="A407" s="10">
         <v>405</v>
       </c>
       <c r="B407" s="9" t="s">
@@ -6751,7 +6755,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="1">
+      <c r="A408" s="10">
         <v>406</v>
       </c>
       <c r="B408" s="9" t="s">
@@ -6759,7 +6763,7 @@
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="1">
+      <c r="A409" s="10">
         <v>407</v>
       </c>
       <c r="B409" s="9" t="s">
@@ -6767,7 +6771,7 @@
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="1">
+      <c r="A410" s="10">
         <v>408</v>
       </c>
       <c r="B410" s="9" t="s">
@@ -6775,7 +6779,7 @@
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="1">
+      <c r="A411" s="10">
         <v>409</v>
       </c>
       <c r="B411" s="9" t="s">
@@ -6783,7 +6787,7 @@
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="1">
+      <c r="A412" s="10">
         <v>410</v>
       </c>
       <c r="B412" s="9" t="s">
@@ -6791,7 +6795,7 @@
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="1">
+      <c r="A413" s="10">
         <v>411</v>
       </c>
       <c r="B413" s="9" t="s">
@@ -6799,7 +6803,7 @@
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="1">
+      <c r="A414" s="10">
         <v>412</v>
       </c>
       <c r="B414" s="9" t="s">
@@ -6807,7 +6811,7 @@
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="1">
+      <c r="A415" s="10">
         <v>413</v>
       </c>
       <c r="B415" s="9" t="s">
@@ -6815,7 +6819,7 @@
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="1">
+      <c r="A416" s="10">
         <v>414</v>
       </c>
       <c r="B416" s="9" t="s">
@@ -6823,7 +6827,7 @@
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="1">
+      <c r="A417" s="10">
         <v>415</v>
       </c>
       <c r="B417" s="9" t="s">
@@ -6831,7 +6835,7 @@
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="1">
+      <c r="A418" s="10">
         <v>416</v>
       </c>
       <c r="B418" s="9" t="s">
@@ -6839,7 +6843,7 @@
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="1">
+      <c r="A419" s="10">
         <v>417</v>
       </c>
       <c r="B419" s="9" t="s">
@@ -6847,7 +6851,7 @@
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="1">
+      <c r="A420" s="10">
         <v>418</v>
       </c>
       <c r="B420" s="9" t="s">
@@ -6855,7 +6859,7 @@
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="1">
+      <c r="A421" s="10">
         <v>419</v>
       </c>
       <c r="B421" s="9" t="s">
@@ -6863,7 +6867,7 @@
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="1">
+      <c r="A422" s="10">
         <v>420</v>
       </c>
       <c r="B422" s="9" t="s">
@@ -6871,7 +6875,7 @@
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="1">
+      <c r="A423" s="10">
         <v>421</v>
       </c>
       <c r="B423" s="9" t="s">
@@ -6879,7 +6883,7 @@
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="1">
+      <c r="A424" s="10">
         <v>422</v>
       </c>
       <c r="B424" s="9" t="s">
@@ -6887,7 +6891,7 @@
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="1">
+      <c r="A425" s="10">
         <v>423</v>
       </c>
       <c r="B425" s="9" t="s">
@@ -6895,7 +6899,7 @@
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="1">
+      <c r="A426" s="10">
         <v>424</v>
       </c>
       <c r="B426" s="9" t="s">
@@ -6903,7 +6907,7 @@
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="1">
+      <c r="A427" s="10">
         <v>425</v>
       </c>
       <c r="B427" s="9" t="s">
@@ -6911,7 +6915,7 @@
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="1">
+      <c r="A428" s="10">
         <v>426</v>
       </c>
       <c r="B428" s="9" t="s">
@@ -6919,7 +6923,7 @@
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="1">
+      <c r="A429" s="10">
         <v>427</v>
       </c>
       <c r="B429" s="9" t="s">
@@ -6927,7 +6931,7 @@
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="1">
+      <c r="A430" s="10">
         <v>428</v>
       </c>
       <c r="B430" s="9" t="s">
@@ -6935,7 +6939,7 @@
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="1">
+      <c r="A431" s="10">
         <v>429</v>
       </c>
       <c r="B431" s="9" t="s">
@@ -6943,7 +6947,7 @@
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="1">
+      <c r="A432" s="10">
         <v>430</v>
       </c>
       <c r="B432" s="9" t="s">
@@ -6951,7 +6955,7 @@
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="1">
+      <c r="A433" s="10">
         <v>431</v>
       </c>
       <c r="B433" s="9" t="s">
@@ -6959,7 +6963,7 @@
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="1">
+      <c r="A434" s="10">
         <v>432</v>
       </c>
       <c r="B434" s="9" t="s">
@@ -6967,7 +6971,7 @@
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="1">
+      <c r="A435" s="10">
         <v>433</v>
       </c>
       <c r="B435" s="9" t="s">
@@ -6975,7 +6979,7 @@
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="1">
+      <c r="A436" s="10">
         <v>434</v>
       </c>
       <c r="B436" s="9" t="s">
@@ -6983,7 +6987,7 @@
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="1">
+      <c r="A437" s="10">
         <v>435</v>
       </c>
       <c r="B437" s="9" t="s">
@@ -6991,7 +6995,7 @@
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="1">
+      <c r="A438" s="10">
         <v>436</v>
       </c>
       <c r="B438" s="9" t="s">
@@ -6999,7 +7003,7 @@
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="1">
+      <c r="A439" s="10">
         <v>437</v>
       </c>
       <c r="B439" s="9" t="s">
@@ -7007,7 +7011,7 @@
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="1">
+      <c r="A440" s="10">
         <v>438</v>
       </c>
       <c r="B440" s="9" t="s">
@@ -7015,7 +7019,7 @@
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="1">
+      <c r="A441" s="10">
         <v>439</v>
       </c>
       <c r="B441" s="9" t="s">
@@ -7023,7 +7027,7 @@
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="1">
+      <c r="A442" s="10">
         <v>440</v>
       </c>
       <c r="B442" s="9" t="s">
@@ -7031,7 +7035,7 @@
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="1">
+      <c r="A443" s="10">
         <v>441</v>
       </c>
       <c r="B443" s="9" t="s">
@@ -7039,7 +7043,7 @@
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="1">
+      <c r="A444" s="10">
         <v>442</v>
       </c>
       <c r="B444" s="9" t="s">
@@ -7047,7 +7051,7 @@
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="1">
+      <c r="A445" s="10">
         <v>443</v>
       </c>
       <c r="B445" s="9" t="s">
@@ -7055,7 +7059,7 @@
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="1">
+      <c r="A446" s="10">
         <v>444</v>
       </c>
       <c r="B446" s="9" t="s">
@@ -7063,7 +7067,7 @@
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="1">
+      <c r="A447" s="10">
         <v>445</v>
       </c>
       <c r="B447" s="9" t="s">
@@ -7071,7 +7075,7 @@
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="1">
+      <c r="A448" s="10">
         <v>446</v>
       </c>
       <c r="B448" s="9" t="s">
@@ -7079,7 +7083,7 @@
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="1">
+      <c r="A449" s="10">
         <v>447</v>
       </c>
       <c r="B449" s="9" t="s">
@@ -7087,7 +7091,7 @@
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="1">
+      <c r="A450" s="10">
         <v>448</v>
       </c>
       <c r="B450" s="9" t="s">
@@ -7095,7 +7099,7 @@
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="1">
+      <c r="A451" s="10">
         <v>449</v>
       </c>
       <c r="B451" s="9" t="s">
@@ -7103,7 +7107,7 @@
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="1">
+      <c r="A452" s="10">
         <v>450</v>
       </c>
       <c r="B452" s="9" t="s">
@@ -7111,7 +7115,7 @@
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="1">
+      <c r="A453" s="10">
         <v>451</v>
       </c>
       <c r="B453" s="9" t="s">
@@ -7119,7 +7123,7 @@
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="1">
+      <c r="A454" s="10">
         <v>452</v>
       </c>
       <c r="B454" s="9" t="s">
@@ -7127,7 +7131,7 @@
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="1">
+      <c r="A455" s="10">
         <v>453</v>
       </c>
       <c r="B455" s="9" t="s">
@@ -7135,7 +7139,7 @@
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="1">
+      <c r="A456" s="10">
         <v>454</v>
       </c>
       <c r="B456" s="9" t="s">
@@ -7143,7 +7147,7 @@
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="1">
+      <c r="A457" s="10">
         <v>455</v>
       </c>
       <c r="B457" s="9" t="s">
@@ -7151,7 +7155,7 @@
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="1">
+      <c r="A458" s="10">
         <v>456</v>
       </c>
       <c r="B458" s="9" t="s">
@@ -7159,7 +7163,7 @@
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="1">
+      <c r="A459" s="10">
         <v>457</v>
       </c>
       <c r="B459" s="9" t="s">
@@ -7167,7 +7171,7 @@
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="1">
+      <c r="A460" s="10">
         <v>458</v>
       </c>
       <c r="B460" s="9" t="s">
@@ -7175,7 +7179,7 @@
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="1">
+      <c r="A461" s="10">
         <v>459</v>
       </c>
       <c r="B461" s="9" t="s">
@@ -7183,7 +7187,7 @@
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="1">
+      <c r="A462" s="10">
         <v>460</v>
       </c>
       <c r="B462" s="9" t="s">
@@ -7191,7 +7195,7 @@
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="1">
+      <c r="A463" s="10">
         <v>461</v>
       </c>
       <c r="B463" s="9" t="s">
@@ -7199,7 +7203,7 @@
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="1">
+      <c r="A464" s="10">
         <v>462</v>
       </c>
       <c r="B464" s="9" t="s">
@@ -7207,7 +7211,7 @@
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="1">
+      <c r="A465" s="10">
         <v>463</v>
       </c>
       <c r="B465" s="9" t="s">
@@ -7215,7 +7219,7 @@
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="1">
+      <c r="A466" s="10">
         <v>464</v>
       </c>
       <c r="B466" s="9" t="s">
@@ -7223,7 +7227,7 @@
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="1">
+      <c r="A467" s="10">
         <v>465</v>
       </c>
       <c r="B467" s="9" t="s">
@@ -7231,7 +7235,7 @@
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="1">
+      <c r="A468" s="10">
         <v>466</v>
       </c>
       <c r="B468" s="9" t="s">
@@ -7239,7 +7243,7 @@
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="1">
+      <c r="A469" s="10">
         <v>467</v>
       </c>
       <c r="B469" s="9" t="s">
@@ -7247,7 +7251,7 @@
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="1">
+      <c r="A470" s="10">
         <v>468</v>
       </c>
       <c r="B470" s="9" t="s">
@@ -7255,7 +7259,7 @@
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="1">
+      <c r="A471" s="10">
         <v>469</v>
       </c>
       <c r="B471" s="9" t="s">
@@ -7263,7 +7267,7 @@
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="1">
+      <c r="A472" s="10">
         <v>470</v>
       </c>
       <c r="B472" s="9" t="s">
@@ -7271,7 +7275,7 @@
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="1">
+      <c r="A473" s="10">
         <v>471</v>
       </c>
       <c r="B473" s="9" t="s">
@@ -7279,7 +7283,7 @@
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="1">
+      <c r="A474" s="10">
         <v>472</v>
       </c>
       <c r="B474" s="9" t="s">
@@ -7287,7 +7291,7 @@
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="1">
+      <c r="A475" s="10">
         <v>473</v>
       </c>
       <c r="B475" s="9" t="s">
@@ -7295,7 +7299,7 @@
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="1">
+      <c r="A476" s="10">
         <v>474</v>
       </c>
       <c r="B476" s="9" t="s">
@@ -7303,7 +7307,7 @@
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="1">
+      <c r="A477" s="10">
         <v>475</v>
       </c>
       <c r="B477" s="9" t="s">
@@ -7311,7 +7315,7 @@
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="1">
+      <c r="A478" s="10">
         <v>476</v>
       </c>
       <c r="B478" s="9" t="s">
@@ -7319,7 +7323,7 @@
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="1">
+      <c r="A479" s="10">
         <v>477</v>
       </c>
       <c r="B479" s="9" t="s">
@@ -7327,7 +7331,7 @@
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="1">
+      <c r="A480" s="10">
         <v>478</v>
       </c>
       <c r="B480" s="9" t="s">
@@ -7335,7 +7339,7 @@
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="1">
+      <c r="A481" s="10">
         <v>479</v>
       </c>
       <c r="B481" s="9" t="s">
@@ -7343,7 +7347,7 @@
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="1">
+      <c r="A482" s="10">
         <v>480</v>
       </c>
       <c r="B482" s="9" t="s">
@@ -7351,7 +7355,7 @@
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="1">
+      <c r="A483" s="10">
         <v>481</v>
       </c>
       <c r="B483" s="9" t="s">
@@ -7359,7 +7363,7 @@
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="1">
+      <c r="A484" s="10">
         <v>482</v>
       </c>
       <c r="B484" s="9" t="s">
@@ -7367,7 +7371,7 @@
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="1">
+      <c r="A485" s="10">
         <v>483</v>
       </c>
       <c r="B485" s="9" t="s">
@@ -7375,7 +7379,7 @@
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="1">
+      <c r="A486" s="10">
         <v>484</v>
       </c>
       <c r="B486" s="9" t="s">
@@ -7383,7 +7387,7 @@
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="1">
+      <c r="A487" s="10">
         <v>485</v>
       </c>
       <c r="B487" s="9" t="s">
@@ -7391,7 +7395,7 @@
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="1">
+      <c r="A488" s="10">
         <v>486</v>
       </c>
       <c r="B488" s="9" t="s">
@@ -7399,7 +7403,7 @@
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="1">
+      <c r="A489" s="10">
         <v>487</v>
       </c>
       <c r="B489" s="9" t="s">
@@ -7407,7 +7411,7 @@
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="1">
+      <c r="A490" s="10">
         <v>488</v>
       </c>
       <c r="B490" s="9" t="s">
@@ -7415,7 +7419,7 @@
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="1">
+      <c r="A491" s="10">
         <v>489</v>
       </c>
       <c r="B491" s="9" t="s">
@@ -7423,7 +7427,7 @@
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="1">
+      <c r="A492" s="10">
         <v>490</v>
       </c>
       <c r="B492" s="9" t="s">
@@ -7431,7 +7435,7 @@
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="1">
+      <c r="A493" s="10">
         <v>491</v>
       </c>
       <c r="B493" s="9" t="s">
@@ -7439,7 +7443,7 @@
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="1">
+      <c r="A494" s="10">
         <v>492</v>
       </c>
       <c r="B494" s="9" t="s">
@@ -7447,7 +7451,7 @@
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="1">
+      <c r="A495" s="10">
         <v>493</v>
       </c>
       <c r="B495" s="9" t="s">
@@ -7455,7 +7459,7 @@
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="1">
+      <c r="A496" s="10">
         <v>494</v>
       </c>
       <c r="B496" s="9" t="s">
@@ -7463,7 +7467,7 @@
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="1">
+      <c r="A497" s="10">
         <v>495</v>
       </c>
       <c r="B497" s="9" t="s">
@@ -7471,7 +7475,7 @@
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="1">
+      <c r="A498" s="10">
         <v>496</v>
       </c>
       <c r="B498" s="9" t="s">
@@ -7479,7 +7483,7 @@
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="1">
+      <c r="A499" s="10">
         <v>497</v>
       </c>
       <c r="B499" s="9" t="s">
@@ -7487,7 +7491,7 @@
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="1">
+      <c r="A500" s="10">
         <v>498</v>
       </c>
       <c r="B500" s="9" t="s">
@@ -7495,7 +7499,7 @@
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="1">
+      <c r="A501" s="10">
         <v>499</v>
       </c>
       <c r="B501" s="9" t="s">
@@ -7503,7 +7507,7 @@
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="1">
+      <c r="A502" s="10">
         <v>500</v>
       </c>
       <c r="B502" s="9" t="s">
@@ -7511,7 +7515,7 @@
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="1">
+      <c r="A503" s="10">
         <v>501</v>
       </c>
       <c r="B503" s="9" t="s">
@@ -7519,7 +7523,7 @@
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="1">
+      <c r="A504" s="10">
         <v>502</v>
       </c>
       <c r="B504" s="9" t="s">
@@ -7527,7 +7531,7 @@
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="1">
+      <c r="A505" s="10">
         <v>503</v>
       </c>
       <c r="B505" s="9" t="s">
@@ -7535,7 +7539,7 @@
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="1">
+      <c r="A506" s="10">
         <v>504</v>
       </c>
       <c r="B506" s="9" t="s">
@@ -7543,7 +7547,7 @@
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="1">
+      <c r="A507" s="10">
         <v>505</v>
       </c>
       <c r="B507" s="9" t="s">
@@ -7551,7 +7555,7 @@
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="1">
+      <c r="A508" s="10">
         <v>506</v>
       </c>
       <c r="B508" s="9" t="s">
@@ -7559,7 +7563,7 @@
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="1">
+      <c r="A509" s="10">
         <v>507</v>
       </c>
       <c r="B509" s="9" t="s">
@@ -7567,7 +7571,7 @@
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="1">
+      <c r="A510" s="10">
         <v>508</v>
       </c>
       <c r="B510" s="9" t="s">
@@ -7575,7 +7579,7 @@
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="1">
+      <c r="A511" s="10">
         <v>509</v>
       </c>
       <c r="B511" s="9" t="s">
@@ -7583,7 +7587,7 @@
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="1">
+      <c r="A512" s="10">
         <v>510</v>
       </c>
       <c r="B512" s="9" t="s">
@@ -7591,7 +7595,7 @@
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="1">
+      <c r="A513" s="10">
         <v>511</v>
       </c>
       <c r="B513" s="9" t="s">
@@ -7599,7 +7603,7 @@
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="1">
+      <c r="A514" s="10">
         <v>512</v>
       </c>
       <c r="B514" s="9" t="s">
@@ -7607,7 +7611,7 @@
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="1">
+      <c r="A515" s="10">
         <v>513</v>
       </c>
       <c r="B515" s="9" t="s">
@@ -7615,7 +7619,7 @@
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="1">
+      <c r="A516" s="10">
         <v>514</v>
       </c>
       <c r="B516" s="9" t="s">
@@ -7623,7 +7627,7 @@
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="1">
+      <c r="A517" s="10">
         <v>515</v>
       </c>
       <c r="B517" s="9" t="s">
@@ -7631,7 +7635,7 @@
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="1">
+      <c r="A518" s="10">
         <v>516</v>
       </c>
       <c r="B518" s="9" t="s">
@@ -7639,7 +7643,7 @@
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="1">
+      <c r="A519" s="10">
         <v>517</v>
       </c>
       <c r="B519" s="9" t="s">
@@ -7647,7 +7651,7 @@
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="1">
+      <c r="A520" s="10">
         <v>518</v>
       </c>
       <c r="B520" s="9" t="s">
@@ -7655,7 +7659,7 @@
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="1">
+      <c r="A521" s="10">
         <v>519</v>
       </c>
       <c r="B521" s="9" t="s">
@@ -7663,7 +7667,7 @@
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="1">
+      <c r="A522" s="10">
         <v>520</v>
       </c>
       <c r="B522" s="9" t="s">
@@ -7671,7 +7675,7 @@
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="1">
+      <c r="A523" s="10">
         <v>521</v>
       </c>
       <c r="B523" s="9" t="s">
@@ -7679,7 +7683,7 @@
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="1">
+      <c r="A524" s="10">
         <v>522</v>
       </c>
       <c r="B524" s="9" t="s">
@@ -7687,7 +7691,7 @@
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="1">
+      <c r="A525" s="10">
         <v>523</v>
       </c>
       <c r="B525" s="9" t="s">
@@ -7695,7 +7699,7 @@
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="1">
+      <c r="A526" s="10">
         <v>524</v>
       </c>
       <c r="B526" s="9" t="s">
@@ -7703,7 +7707,7 @@
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="1">
+      <c r="A527" s="10">
         <v>525</v>
       </c>
       <c r="B527" s="9" t="s">
@@ -7711,7 +7715,7 @@
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="1">
+      <c r="A528" s="10">
         <v>526</v>
       </c>
       <c r="B528" s="9" t="s">
@@ -7719,7 +7723,7 @@
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="1">
+      <c r="A529" s="10">
         <v>527</v>
       </c>
       <c r="B529" s="9" t="s">
@@ -7727,7 +7731,7 @@
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="1">
+      <c r="A530" s="10">
         <v>528</v>
       </c>
       <c r="B530" s="9" t="s">
@@ -7735,7 +7739,7 @@
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="1">
+      <c r="A531" s="10">
         <v>529</v>
       </c>
       <c r="B531" s="9" t="s">
